--- a/docs/22_cera-logical-data-model.xlsx
+++ b/docs/22_cera-logical-data-model.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>rev.2.1 (2026-09-17, T-079) · 기준: docs/21 개념 모델 rev.3 (승인) · 짝 문서: docs/22_cera-logical-data-model.md · 사용자 결정 D-1~D-5 전부 CLOSED · 분류(Classification)와 변경 방식(Mutation Policy)은 서로 다른 축이다</t>
+          <t>rev.2.2 최종 정리 (2026-09-18, T-079) · 기준: docs/21 개념 모델 rev.3 (승인) · 짝 문서: docs/22_cera-logical-data-model.md · 사용자 결정 D-1~D-5 전부 CLOSED · 분류(Classification)와 변경 방식(Mutation Policy)은 서로 다른 축이다 · rev.2.2: 기술 운영 표 system_error 추가</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="9" t="inlineStr"/>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (결과 5컬럼)</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (검토 4컬럼)</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -2966,84 +2966,82 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
+          <t>system_error</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>시스템·연동 오류 기록</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>APPEND_ONLY</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>MVP · rev.2.2</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>error_id</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>중요한 시스템/외부 연동 오류를 DB 에서 찾기 위한 기술 운영 표. 업무 개념이 아니다 (docs/23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>09_감사운영</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>시나리오</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>SIMULATION_ONLY</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>CONTROLLED_UPDATE</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>재생 시나리오. 제품 도메인이 아니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>10_OpenDecisions</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>exception_case</t>
-        </is>
-      </c>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t>예외 운영 Case</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="10" t="inlineStr">
-        <is>
-          <t>CLOSED FOR MVP - 만들지 않는다</t>
-        </is>
-      </c>
-      <c r="H63" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="12" t="inlineStr">
-        <is>
-          <t>Event -&gt; Risk -&gt; RecoveryRun -&gt; Communication -&gt; Reply -&gt; Re-run 폐쇄 루프에 필수가 아니다. 현재는 파생 조회  [E-36 · L-10 · D-5]</t>
         </is>
       </c>
     </row>
@@ -3060,131 +3058,178 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
+          <t>exception_case</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>예외 운영 Case</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>CLOSED FOR MVP - 만들지 않는다</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>Event -&gt; Risk -&gt; RecoveryRun -&gt; Communication -&gt; Reply -&gt; Re-run 폐쇄 루프에 필수가 아니다. 현재는 파생 조회  [E-36 · L-10 · D-5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>10_OpenDecisions</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
           <t>operational_plan_batch</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>계획 업로드 묶음</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>CLOSED - 만들지 않는다</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H65" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="12" t="inlineStr">
+      <c r="I65" s="12" t="inlineStr">
         <is>
           <t>raw_input 1행이 이미 업로드 1건이고 그 배치의 plan.* 사건이 같은 raw_input_id 를 공유한다  [E-35 · L-9 · D-4]</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>만들지 않은 것</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>이유</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>truck (개별 차량)</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>MVP 기능이 풀 + 슬롯별 가용량으로 성립한다 (E-39, Q-57)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>truck (개별 차량)</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>값 객체. cost_line_item 의 금액 컬럼 묶음 (Q-58)</t>
+          <t>MVP 기능이 풀 + 슬롯별 가용량으로 성립한다 (E-39, Q-57)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>phase / container_phase</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>파생. 원본으로 저장하지 않는다 (안티패턴 1)</t>
+          <t>값 객체. cost_line_item 의 금액 컬럼 묶음 (Q-58)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>slot_pool</t>
+          <t>phase / container_phase</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>터미널의 자원 단위. 슬롯 가용은 사실</t>
+          <t>파생. 원본으로 저장하지 않는다 (안티패턴 1)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>destination / carrier</t>
+          <t>slot_pool</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>관계에 붙은 역할. 별도 테이블 아님</t>
+          <t>터미널의 자원 단위. 슬롯 가용은 사실</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>activity_timeline</t>
+          <t>destination / carrier</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>다섯 원본을 합친 조회 뷰</t>
+          <t>관계에 붙은 역할. 별도 테이블 아님</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
+          <t>activity_timeline</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>다섯 원본을 합친 조회 뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
           <t>code_group / code_value</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>코드 테이블은 물리 설계에서 형태를 정한다 (18절)</t>
         </is>
@@ -3201,7 +3246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3220,6 +3265,11 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4022,7 +4072,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>scenario</t>
+          <t>system_error</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -4032,7 +4082,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>시나리오</t>
+          <t>시스템·연동 오류 기록</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -4042,7 +4092,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>SIMULATION_ONLY</t>
+          <t>EVIDENCE</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -4052,7 +4102,7 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · rev.2.2</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -4062,7 +4112,7 @@
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>CONTROLLED_UPDATE</t>
+          <t>APPEND_ONLY</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4124,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>재생 시나리오. 제품 도메인이 아니다</t>
+          <t>CERA 안이나 외부 시스템 호출에서 난 중요한 기술 오류를 DB 에서 찾기 위한 기술 운영(관측성) 표. 업무 도메인 개념이 아니다 (docs/21 밖, 행동 규칙 정본 docs/23)</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4136,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>시뮬레이션 전용 테이블을 따로 만들지 않는다. 같은 테이블 + is_simulated + scenario_id</t>
+          <t>event(현실 사실) · audit_log(누가 무엇을 했나) · send_attempt(이 시도가 어떻게 끝났나)와 다르다. 모든 로그를 넣지 않는다 - 중요한 ERROR·외부 연동 실패·예상 밖 5xx·작업 실패만. 비밀값·토큰·메일 본문·전체 스택 트레이스 금지(raw_log_ref 참조만). 행을 고치지 않는다 - 대응 이력 표는 만들지 않았다</t>
         </is>
       </c>
     </row>
@@ -4098,37 +4148,102 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>시나리오 id</t>
+          <t>오류 id</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>시나리오명</t>
+          <t>발생 시각</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>데이터 팩 참조</t>
+          <t>구성요소</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>기준 시각</t>
+          <t>작업</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>경계</t>
         </is>
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>오류 분류</t>
+        </is>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>오류 코드</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>안전한 메시지</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>예외 종류</t>
+        </is>
+      </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>요청 id</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>추적 id</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>대상 외부 시스템</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>HTTP 상태</t>
+        </is>
+      </c>
+      <c r="P30" s="16" t="inlineStr">
+        <is>
+          <t>재시도 가능</t>
+        </is>
+      </c>
+      <c r="Q30" s="16" t="inlineStr">
+        <is>
+          <t>관련 개체 종류</t>
+        </is>
+      </c>
+      <c r="R30" s="16" t="inlineStr">
+        <is>
+          <t>관련 개체 id</t>
+        </is>
+      </c>
+      <c r="S30" s="16" t="inlineStr">
+        <is>
+          <t>로그 참조</t>
+        </is>
+      </c>
+      <c r="T30" s="16" t="inlineStr">
+        <is>
+          <t>시뮬레이션</t>
+        </is>
+      </c>
+      <c r="U30" s="16" t="inlineStr">
+        <is>
+          <t>시나리오</t>
         </is>
       </c>
     </row>
@@ -4140,37 +4255,102 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
+          <t>error_id</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>occurred_at</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>service_name</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>component_name</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>operation_name</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>error_boundary</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
+        <is>
+          <t>error_category</t>
+        </is>
+      </c>
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>error_code</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>safe_error_message</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="inlineStr">
+        <is>
+          <t>exception_type</t>
+        </is>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>request_id</t>
+        </is>
+      </c>
+      <c r="M31" s="19" t="inlineStr">
+        <is>
+          <t>trace_id</t>
+        </is>
+      </c>
+      <c r="N31" s="19" t="inlineStr">
+        <is>
+          <t>target_system</t>
+        </is>
+      </c>
+      <c r="O31" s="19" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="P31" s="19" t="inlineStr">
+        <is>
+          <t>retryable</t>
+        </is>
+      </c>
+      <c r="Q31" s="19" t="inlineStr">
+        <is>
+          <t>related_entity_type</t>
+        </is>
+      </c>
+      <c r="R31" s="19" t="inlineStr">
+        <is>
+          <t>related_entity_id</t>
+        </is>
+      </c>
+      <c r="S31" s="19" t="inlineStr">
+        <is>
+          <t>raw_log_ref</t>
+        </is>
+      </c>
+      <c r="T31" s="19" t="inlineStr">
+        <is>
+          <t>is_simulated</t>
+        </is>
+      </c>
+      <c r="U31" s="20" t="inlineStr">
+        <is>
           <t>scenario_id</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>scenario_name</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>data_pack_ref</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>as_of_base</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>is_active</t>
         </is>
       </c>
     </row>
@@ -4182,37 +4362,102 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>STRING(30)</t>
+          <t>STRING(40)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>STRING(60)</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
           <t>STRING(100)</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>STRING(100)</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>STRING(60)</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>STRING(500)</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>STRING(200)</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>STRING(64)</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>STRING(64)</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>STRING(40)</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
         <is>
           <t>STRING(300)</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>STRING(300)</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="T32" s="6" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="U32" s="6" t="inlineStr">
+        <is>
+          <t>REF(scenario)</t>
         </is>
       </c>
     </row>
@@ -4234,27 +4479,92 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>API_REQUEST / INTEGRATION / BACKGROUND_JOB</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 값 목록 미확정 (Q-66)</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 정규화 코드</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 비밀값·본문·스택 금지</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 업무 correlation_id 와 다름</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / GMAIL / UNIPASS / DATA_GO_KR / LLM_PROVIDER …</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 분류 규칙이 판정</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 다형 참조</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / DB FK 없음</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 외부 로그 위치만</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>is_simulated=true 일 때만</t>
         </is>
       </c>
     </row>
@@ -4266,35 +4576,488 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>ERR-000001</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T10:05+09:00</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>back-worker</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>channels.gmail</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>send_message</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>INTEGRATION</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>EXTERNAL_SERVER_ERROR</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>GMAIL_SERVER_ERROR</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Gmail send returned 503</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>(예외 클래스명)</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>req-(예시)</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>trc-(예시)</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>GMAIL</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>SEND_ATTEMPT</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>SND-0001</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>log://(예시)</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>예시 2</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>ERR-000002</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T10:40+09:00</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>back-api</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>extraction.email</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>parse_reply</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>INTEGRATION</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>EXTERNAL_RESPONSE_INVALID</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>EXTERNAL_RESPONSE_INVALID</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LLM 응답이 추출 스키마와 맞지 않음</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>(예외 클래스명)</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>req-(예시)</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>trc-(예시)</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>LLM_PROVIDER</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>EXTRACTION</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>EXT-0009</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>log://(예시)</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
           <t>SCN-BUSAN-WH-01</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>영문 테이블명</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>한글 테이블명</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>SIMULATION_ONLY</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>변경 방식</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>CONTROLLED_UPDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>재생 시나리오. 제품 도메인이 아니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>시뮬레이션 전용 테이블을 따로 만들지 않는다. 같은 테이블 + is_simulated + scenario_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>한글 필드명</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>시나리오 id</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>시나리오명</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>데이터 팩 참조</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>기준 시각</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>생성 시각</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>영문 필드명</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>scenario_name</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>data_pack_ref</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>as_of_base</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>STRING(30)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>STRING(100)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>STRING(300)</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>STRING(300)</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>예시 1</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>SCN-BUSAN-WH-01</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>부산 창고 수용량 예외 30대</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Prototype 기준 시나리오</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>data/scenarios/busan-wh-capacity-01/</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T06:00+09:00</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>2026-09-15T00:00+09:00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -4311,7 +5074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4325,7 +5088,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>사용자 결정 결과 · 열린 질문 판정 (rev.2)</t>
+          <t>사용자 결정 결과 · 열린 질문 판정 (rev.2.2 최종 정리)</t>
         </is>
       </c>
     </row>
@@ -4839,7 +5602,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>question_item 이 target_entity_*/target_fact_key 를 갖고 ask_id 로 단건 조회</t>
+          <t>question_item 이 target_entity_type/id · target_fact_key · target_applicability_scope_type/ref(rev.2.1) 를 질문 생성 시 확정하고 ask_id 로 단건 조회. 개체·사실 키·적용 범위가 모두 그 행에서 나오며 LLM 은 범위를 만지지 않는다</t>
         </is>
       </c>
     </row>
@@ -5195,101 +5958,137 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="23" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>Q-66</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>system_error 의 오류 분류·코드 값 목록</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>OPEN - rev.2.2 신규</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>예시(GMAIL_TIMEOUT · GMAIL_RATE_LIMITED · GMAIL_AUTH_EXPIRED · EXTERNAL_RESPONSE_INVALID)만 적었다. 전체 목록은 T-069 구현 계획·구현에서 정한다 (docs/23 6절)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t>[4] 이번 단계에서 정하지 않는 것</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>DB 제품 (PostgreSQL / MySQL / SQLite)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DB 제품 (PostgreSQL / MySQL / SQLite)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>실제 CREATE TABLE SQL / 마이그레이션</t>
+          <t>ORM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>인덱스·파티션·복제</t>
+          <t>실제 CREATE TABLE SQL / 마이그레이션</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>API endpoint</t>
+          <t>인덱스·파티션·복제</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>LLM 공급자·모델</t>
+          <t>API endpoint</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>솔버와 그 내부 표현</t>
+          <t>LLM 공급자·모델</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>위험·신선도·근거 강도의 실제 임계값</t>
+          <t>솔버와 그 내부 표현</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>plan_decision.decision_type 의 값 목록</t>
+          <t>위험·신선도·근거 강도의 실제 임계값</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>applicability_scope_type 값 목록 (L-14)</t>
+          <t>plan_decision.decision_type 의 값 목록</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>복구 맥락 식별자 (L-13)</t>
+          <t>applicability_scope_type 값 목록 (L-14)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>bl 의 실제 UNIQUE 제약 (L-16)</t>
+          <t>복구 맥락 식별자 (L-13)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
+          <t>bl 의 실제 UNIQUE 제약 (L-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
           <t>적용 범위 사이의 우선순위 규칙 (L-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>system_error 오류 분류·코드 값 목록 (Q-66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Backend 언어·프레임워크 (ADR-031 Proposed, docs/23)</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11838,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>rev.2: source_tier 제거(근거 강도는 계산 결과 -&gt; canonical_fact). 원천 축만 남긴다. 적용 범위(scope)와 유효 기간(validity)은 다른 축이다. 예시 3 = 운영자의 '이번 건만 0원'</t>
+          <t>rev.2: source_tier 제거(근거 강도는 계산 결과 -&gt; canonical_fact). 원천 축만 남긴다. 적용 범위(scope)와 유효 기간(validity)은 다른 축이다. 예시 3 = 운영자의 '이번 건만 0원' / rev.2.2: 복구 맥락 참조는 자리표시자 &lt;RECOVERY_CONTEXT_REF&gt; 로 적는다 - 별도 RecoveryContext 표도, recovery_run id 라는 뜻도 아니다. 식별 방식은 L-13 이 정한다</t>
         </is>
       </c>
     </row>
@@ -11859,7 +12658,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -13100,7 +13899,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -14386,7 +15185,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr"/>
@@ -17791,7 +18590,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -18205,7 +19004,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -18290,7 +19089,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>사실이 없어 마스터 기본값으로 계산했다면 그 값을 남긴다. 마스터는 수정 가능하므로 나중에 고치면 과거 실행이 재현되지 않는다. tariff_rule 은 불변 판이라 id 참조로 충분하다</t>
+          <t>사실이 없어 마스터 기본값으로 계산했다면 그 값을 남긴다. 마스터는 수정 가능하므로 나중에 고치면 과거 실행이 재현되지 않는다. tariff_rule 은 불변 판이라 id 참조로 충분하다 / rev.2.2: value_path 는 PK 일부라 NOT NULL. 예시 2 의 &lt;WHOLE_ROW&gt; 는 '행 전체' 를 뜻하는 자리표시자이고 실제 문자열은 T-080 에서 정한다</t>
         </is>
       </c>
     </row>
@@ -18478,7 +19277,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용 / 컬럼 이름</t>
+          <t>NOT NULL / MASTER_DEFAULT = 컬럼 경로 · 행/판 전체 = 논리적 '전체' 표시 (물리 문자열은 T-080)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -18572,7 +19371,11 @@
           <t>TRF-0001</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>&lt;WHOLE_ROW&gt;</t>
+        </is>
+      </c>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr">
@@ -20403,7 +21206,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -20473,7 +21276,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
@@ -20547,7 +21350,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -23563,7 +24366,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -24960,7 +25763,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>rev.2.1: 행 종류별 필수 컬럼이 다르다. APPROVED = 내용·수신자·지문·구조화 값 사본 필수. REJECTED/REVISION_REQUESTED = 사유 필수, 내용 사본은 선택. REVOKED/INVALIDATED = 대상 + 사유 종류만 필수이고 승인 사본을 새로 요구하지 않는다. 만료는 expires_at(만들 때 정함). 어떤 행도 UPDATE 하지 않는다</t>
+          <t>rev.2.1·rev.2.2: 행 종류별 필수 컬럼이 다르다. APPROVED = approved_content_hash · approved_to_address_id 필수 + 메시지에 값이 있는 범위에서 제목·본문·구조화 값 사본 필수. REJECTED/REVISION_REQUESTED = reason 필수, 사본 조건을 적용하지 않는다. REVOKED/INVALIDATED = invalidates_approval_id + invalidation_cause 필수, 새 지문·사본 불필요, 대상은 같은 message_id 의 기존 APPROVED. 만료는 expires_at(만들 때 정함). 어떤 행도 UPDATE 하지 않는다</t>
         </is>
       </c>
     </row>
@@ -25243,17 +26046,17 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>APPROVED 면 필수 / 사본</t>
+          <t>APPROVED 이고 원 메시지에 값이 있으면 필수 / 사본 (값이 없는 메시지에 빈 사본을 요구하지 않는다)</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>APPROVED 면 필수 / 사본</t>
+          <t>APPROVED 이고 원 메시지에 값이 있으면 필수 / 사본 (값이 없는 메시지에 빈 사본을 요구하지 않는다)</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용</t>
+          <t>NULL 허용 / 계획 기반 메시지의 APPROVED 면 필수</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -25268,7 +26071,7 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용</t>
+          <t>REJECTED·REVISION_REQUESTED 면 필수 / 무효화일 때 권장</t>
         </is>
       </c>
     </row>
@@ -25798,7 +26601,7 @@
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (결과 5컬럼)</t>
         </is>
       </c>
     </row>
@@ -25822,7 +26625,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>rev.2.1: 지문 비교 대상이 종류별로 다르다. BUSINESS = 유효한 승인의 approved_content_hash, CONTACT_VERIFICATION = 그 메시지 자신의 content_hash. 어느 쪽도 '작성한 내용 != 보낸 내용' 은 허용하지 않는다. approval_id 는 메시지 종류에 따른 조건부 필수. UNKNOWN 을 성공·실패로 접지 않는다</t>
+          <t>rev.2.2: 식별·요청 9컬럼(send_attempt_id·message_id·approval_id·attempt_no·idempotency_key·channel_connection_id·sent_content_hash·started_at·is_simulated)은 불변. 결과 5컬럼(finished_at·result·error_code·error_message·provider_message_id)만 호출 뒤 한 번 기록. 재시도는 새 행. 기술 오류 상세는 system_error. rev.2.1: 지문 비교 대상이 종류별로 다르다. BUSINESS = 유효한 승인의 approved_content_hash, CONTACT_VERIFICATION = 그 메시지 자신의 content_hash. UNKNOWN 을 성공·실패로 접지 않는다</t>
         </is>
       </c>
     </row>
@@ -26100,17 +26903,17 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL / 외부 호출 전에 기록</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용</t>
+          <t>NULL 허용 / 결과 기록 때 한 번</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>SUCCESS / RETRYABLE_FAILURE / PERMANENT_FAILURE / UNKNOWN</t>
+          <t>NULL = 결과 기록 전 / SUCCESS / RETRYABLE_FAILURE / PERMANENT_FAILURE / UNKNOWN - 한 번만</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
@@ -26668,7 +27471,7 @@
       </c>
       <c r="K97" s="9" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (검토 4컬럼)</t>
         </is>
       </c>
     </row>
@@ -26692,7 +27495,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>신원·권한·근거 강도·상태 확정·숫자는 여기서 정하지 않는다 (ADR-026·029)</t>
+          <t>rev.2.2: 추출 결과(후보 값·인용·모델 판·프롬프트 판 등)는 불변. 검토 4컬럼(review_status·reviewed_by_actor_id·reviewed_at·created_event_id)만 PENDING -&gt; ACCEPTED/REJECTED/SUPERSEDED 한 방향 한 번. 신원·권한·근거 강도·상태 확정·숫자는 여기서 정하지 않는다 (ADR-026·029)</t>
         </is>
       </c>
     </row>
@@ -27020,7 +27823,7 @@
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>PENDING / ACCEPTED / REJECTED / SUPERSEDED</t>
+          <t>PENDING / ACCEPTED / REJECTED / SUPERSEDED - 한 방향 한 번</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
@@ -27035,7 +27838,7 @@
       </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용</t>
+          <t>NULL 허용 / ACCEPTED 면 필수</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">

--- a/docs/22_cera-logical-data-model.xlsx
+++ b/docs/22_cera-logical-data-model.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>rev.2.2 최종 정리 (2026-09-18, T-079) · 기준: docs/21 개념 모델 rev.3 (승인) · 짝 문서: docs/22_cera-logical-data-model.md · 사용자 결정 D-1~D-5 전부 CLOSED · 분류(Classification)와 변경 방식(Mutation Policy)은 서로 다른 축이다 · rev.2.2: 기술 운영 표 system_error 추가</t>
+          <t>rev.2.3 논리 모델 후속 T-081 DONE (2026-09-21, 사용자 최종 승인). docs/05 4.2 대조로 누락 13건 복구 + ADR-020 상태 차원 복구. 표 +1. 흐름 검증 47개 PASS</t>
         </is>
       </c>
     </row>
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>이번 단계에서 설계한 테이블</t>
+          <t>이번 단계에서 설계한 테이블 (rev.2.3 에서 event_verification_target +1)</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" s="9" t="inlineStr"/>
     </row>
@@ -1526,37 +1526,27 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>canonical_fact</t>
+          <t>event_verification_target</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>현재 사실</t>
+          <t>확인 대상 연결</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>DERIVED_MATERIALIZED</t>
+          <t>SOURCE_OF_TRUTH</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>REBUILDABLE</t>
+          <t>APPEND_ONLY</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>entity_type + entity_id + fact_key + applicability_scope_type + applicability_scope_ref + is_simulated</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>한 사실의 현재 결론. 전부 지워도 event 로부터 복원되어야 한다</t>
+          <t>MVP · rev.2.3</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1561,12 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>conflict</t>
+          <t>canonical_fact</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>충돌</t>
+          <t>현재 사실</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1596,12 +1586,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>conflict_id</t>
+          <t>entity_type + entity_id + fact_key + applicability_scope_type + applicability_scope_ref + is_simulated</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>자동으로 정할 근거가 없는 차이. 같은 적용 범위 안에서만 생긴다</t>
+          <t>한 사실의 현재 결론. 전부 지워도 event 로부터 복원되어야 한다</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1606,12 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>verification_request</t>
+          <t>conflict</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>확인 요청</t>
+          <t>충돌</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1641,12 +1631,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>verification_request_id</t>
+          <t>conflict_id</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>사람에게 물어야 할 항목. 재계산으로 다시 만들어진다</t>
+          <t>자동으로 정할 근거가 없는 차이. 같은 적용 범위 안에서만 생긴다</t>
         </is>
       </c>
     </row>
@@ -1661,22 +1651,22 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>verification_request_handling</t>
+          <t>verification_request</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>확인 요청 처리 기록</t>
+          <t>확인 요청</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>DECISION_RECORD</t>
+          <t>DERIVED_MATERIALIZED</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>REBUILDABLE</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -1686,12 +1676,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>handling_id</t>
+          <t>verification_request_id</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>사람의 열람/미룸/처리 이력. 재계산으로 지워지지 않는다</t>
+          <t>사람에게 물어야 할 항목. 재계산으로 다시 만들어진다</t>
         </is>
       </c>
     </row>
@@ -1701,27 +1691,27 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>05_계약요율</t>
+          <t>04_사건상태</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>verification_request_handling</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>계약</t>
+          <t>확인 요청 처리 기록</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>DECISION_RECORD</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>CONTROLLED_UPDATE</t>
+          <t>APPEND_ONLY</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -1731,12 +1721,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>contract_id</t>
+          <t>handling_id</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>계약 원문 참조. 원문 자체는 저장소에 넣지 않는다</t>
+          <t>사람의 열람/미룸/처리 이력. 재계산으로 지워지지 않는다</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1741,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>tariff_rule</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>요율 규칙</t>
+          <t>계약</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1766,7 +1756,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>VERSION_REPLACEMENT</t>
+          <t>CONTROLLED_UPDATE</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -1776,12 +1766,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>tariff_rule_id</t>
+          <t>contract_id</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>확정된 요율/무료기간 계산 규칙. 수정하지 않고 새 판으로 교체한다</t>
+          <t>계약 원문 참조. 원문 자체는 저장소에 넣지 않는다</t>
         </is>
       </c>
     </row>
@@ -1796,37 +1786,37 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>commercial_offer</t>
+          <t>tariff_rule</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>요율 규칙</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>EVIDENCE</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>CONTROLLED_UPDATE (offer_status)</t>
+          <t>VERSION_REPLACEMENT</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>MVP · D-2</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>offer_id</t>
+          <t>tariff_rule_id</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>누가 언제 무엇을 어떤 조건으로 제안했는가. 계산 정본이 아니다</t>
+          <t>확정된 요율/무료기간 계산 규칙. 수정하지 않고 새 판으로 교체한다</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1831,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>commercial_offer_item</t>
+          <t>commercial_offer</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>제안 줄</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1856,7 +1846,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>CONTROLLED_UPDATE (offer_status)</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -1866,12 +1856,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>offer_item_id</t>
+          <t>offer_id</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>제안 한 건의 금액 줄. 외화는 5값 묶음으로 재현 가능하게 남긴다</t>
+          <t>누가 언제 무엇을 어떤 조건으로 제안했는가. 계산 정본이 아니다</t>
         </is>
       </c>
     </row>
@@ -1881,22 +1871,22 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>06_계획최적화</t>
+          <t>05_계약요율</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>planning_snapshot</t>
+          <t>commercial_offer_item</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>계획 입력 스냅샷</t>
+          <t>제안 줄</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>PERSISTED_OUTPUT</t>
+          <t>EVIDENCE</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -1906,17 +1896,17 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · D-2</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>snapshot_id</t>
+          <t>offer_item_id</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>엔진 입력을 고정한 묶음. 이것이 있어야 같은 결과를 다시 만든다</t>
+          <t>제안 한 건의 금액 줄. 외화는 5값 묶음으로 재현 가능하게 남긴다</t>
         </is>
       </c>
     </row>
@@ -1931,12 +1921,12 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>planning_snapshot_fact</t>
+          <t>planning_snapshot</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>스냅샷 사실</t>
+          <t>계획 입력 스냅샷</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1956,12 +1946,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>snapshot_id + entity_type + entity_id + fact_key + applicability_scope_type + applicability_scope_ref</t>
+          <t>snapshot_id</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>스냅샷에 담긴 사실의 값 사본. FK 로만 가리키지 않는다</t>
+          <t>엔진 입력을 고정한 묶음. 이것이 있어야 같은 결과를 다시 만든다</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1966,12 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>planning_snapshot_constraint</t>
+          <t>planning_snapshot_fact</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>스냅샷 계획 조건</t>
+          <t>스냅샷 사실</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -2001,12 +1991,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>snapshot_id + constraint_id</t>
+          <t>snapshot_id + entity_type + entity_id + fact_key + applicability_scope_type + applicability_scope_ref</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>계산 당시 걸려 있던 운영자 계획 조건의 값 사본 (rev.2 신규)</t>
+          <t>스냅샷에 담긴 사실의 값 사본. FK 로만 가리키지 않는다</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2011,12 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>planning_snapshot_input</t>
+          <t>planning_snapshot_constraint</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>스냅샷 그 밖의 입력</t>
+          <t>스냅샷 계획 조건</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -2046,12 +2036,12 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>snapshot_id + input_kind + source_table + source_key + value_path</t>
+          <t>snapshot_id + constraint_id</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>사실도 계획 조건도 아닌데 계산을 바꾸는 입력 (rev.2 신규)</t>
+          <t>계산 당시 걸려 있던 운영자 계획 조건의 값 사본 (rev.2 신규)</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2056,12 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>recovery_run</t>
+          <t>planning_snapshot_input</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>복구 계산 실행</t>
+          <t>스냅샷 그 밖의 입력</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2091,12 +2081,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>run_id</t>
+          <t>snapshot_id + input_kind + source_table + source_key + value_path</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>복구 계획 계산 1회 = 계획 버전. 솔버 이름/모델 형식은 여기서 정하지 않는다</t>
+          <t>사실도 계획 조건도 아닌데 계산을 바꾸는 입력 (rev.2 신규)</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2101,12 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>assignment</t>
+          <t>recovery_run</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>배정</t>
+          <t>복구 계산 실행</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2136,12 +2126,12 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>run_id</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>이 컨테이너를 이 경로로. 실행 여부는 여기 컬럼이 아니다</t>
+          <t>복구 계획 계산 1회 = 계획 버전. 솔버 이름/모델 형식은 여기서 정하지 않는다</t>
         </is>
       </c>
     </row>
@@ -2156,17 +2146,17 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>plan_decision</t>
+          <t>assignment</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>계획 결정 기록</t>
+          <t>배정</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>DECISION_RECORD</t>
+          <t>PERSISTED_OUTPUT</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -2181,12 +2171,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>plan_decision_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>A-16 게이트. 사실 확인·메시지 승인과 분리된 별개의 게이트</t>
+          <t>이 컨테이너를 이 경로로. 실행 여부는 여기 컬럼이 아니다</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2191,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>operator_planning_constraint</t>
+          <t>plan_decision</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>운영자 계획 조건</t>
+          <t>계획 결정 기록</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2226,12 +2216,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>constraint_id</t>
+          <t>plan_decision_id</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>운영자가 최적화에 준 사용/제외/선호/한도 조건. 현실 사실이 아니다 (E-37)</t>
+          <t>A-16 게이트. 사실 확인·메시지 승인과 분리된 별개의 게이트</t>
         </is>
       </c>
     </row>
@@ -2241,22 +2231,22 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>07_위험비용</t>
+          <t>06_계획최적화</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>risk_assessment</t>
+          <t>operator_planning_constraint</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>위험 평가</t>
+          <t>운영자 계획 조건</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>PERSISTED_OUTPUT</t>
+          <t>DECISION_RECORD</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -2271,12 +2261,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>risk_assessment_id</t>
+          <t>constraint_id</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>규칙으로 판정한 결정론적 결과. 확률이 아니다 (FR-RSK-05)</t>
+          <t>운영자가 최적화에 준 사용/제외/선호/한도 조건. 현실 사실이 아니다 (E-37)</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2281,12 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>cost_result</t>
+          <t>risk_assessment</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>비용 계산 결과</t>
+          <t>위험 평가</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -2316,12 +2306,12 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>cost_result_id</t>
+          <t>risk_assessment_id</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>계획별 비용 계산 결과 묶음. MVP 는 예상 비용과 계획 비용 두 가지뿐이다</t>
+          <t>규칙으로 판정한 결정론적 결과. 확률이 아니다 (FR-RSK-05)</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2326,12 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>cost_line_item</t>
+          <t>cost_result</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>비용 줄</t>
+          <t>비용 계산 결과</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -2361,12 +2351,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>cost_line_item_id</t>
+          <t>cost_result_id</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>비용 내역 한 줄. 필수 부모는 cost_result 하나뿐이다 (Q-60)</t>
+          <t>계획별 비용 계산 결과 묶음. MVP 는 예상 비용과 계획 비용 두 가지뿐이다</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2371,12 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>cost_line_link</t>
+          <t>cost_line_item</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>비용 줄 귀속·근거</t>
+          <t>비용 줄</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2406,12 +2396,12 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>cost_line_item_id + link_role + target_type + target_id</t>
+          <t>cost_line_item_id</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>한 줄이 누구에게 귀속되고 무엇을 근거로 하는지 (Q-60)</t>
+          <t>비용 내역 한 줄. 필수 부모는 cost_result 하나뿐이다 (Q-60)</t>
         </is>
       </c>
     </row>
@@ -2421,27 +2411,27 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>08_외부통신</t>
+          <t>07_위험비용</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>comm_thread</t>
+          <t>cost_line_link</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>비용 줄 귀속·근거</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>SOURCE_OF_TRUTH</t>
+          <t>PERSISTED_OUTPUT</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>CONTROLLED_UPDATE (thread_status · last_activity_at)</t>
+          <t>APPEND_ONLY</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -2451,12 +2441,12 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>thread_id</t>
+          <t>cost_line_item_id + link_role + target_type + target_id</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>문의 대화 한 건. 회신을 붙일 단위</t>
+          <t>한 줄이 누구에게 귀속되고 무엇을 근거로 하는지 (Q-60)</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2461,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>question_item</t>
+          <t>comm_thread</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>질문 항목</t>
+          <t>대화</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -2486,7 +2476,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>CONTROLLED_UPDATE (question_status)</t>
+          <t>CONTROLLED_UPDATE (thread_status · last_activity_at)</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -2496,12 +2486,12 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>question_item_id</t>
+          <t>thread_id</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>그 스레드에서 물은 질문 하나. 회신 값을 사실 키로 되붙이는 결정론 축 (L-1)</t>
+          <t>문의 대화 한 건. 회신을 붙일 단위</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2506,12 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>comm_message</t>
+          <t>question_item</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>메시지</t>
+          <t>질문 항목</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -2531,7 +2521,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>IMMUTABLE_AFTER_CREATE + CACHE_UPDATE</t>
+          <t>CONTROLLED_UPDATE (question_status)</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -2541,12 +2531,12 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>message_id</t>
+          <t>question_item_id</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>보낸/받은 한 통. 내용은 수정하지 않고 상태 포인터만 갱신한다</t>
+          <t>그 스레드에서 물은 질문 하나. 회신 값을 사실 키로 되붙이는 결정론 축 (L-1)</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2551,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>comm_message_structured_field</t>
+          <t>comm_message</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>메시지 구조화 값</t>
+          <t>메시지</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2576,7 +2566,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>IMMUTABLE_AFTER_CREATE + CACHE_UPDATE</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -2586,12 +2576,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>message_id + field_key</t>
+          <t>message_id</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>메시지에 실리는 숫자와 그 출처 (rev.2 신규). 숫자는 계획에서 주입되고 AI 는 문장만 쓴다</t>
+          <t>보낸/받은 한 통. 내용은 수정하지 않고 상태 포인터만 갱신한다</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2596,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>comm_message_question</t>
+          <t>comm_message_structured_field</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>메시지 질문 연결</t>
+          <t>메시지 구조화 값</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2631,12 +2621,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>message_id + question_item_id</t>
+          <t>message_id + field_key</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>한 메시지에 여러 질문, 한 질문이 재발송으로 여러 메시지에</t>
+          <t>메시지에 실리는 숫자와 그 출처 (rev.2 신규). 숫자는 계획에서 주입되고 AI 는 문장만 쓴다</t>
         </is>
       </c>
     </row>
@@ -2651,17 +2641,17 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>message_approval</t>
+          <t>comm_message_question</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>메시지 승인</t>
+          <t>메시지 질문 연결</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>DECISION_RECORD</t>
+          <t>SOURCE_OF_TRUTH</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -2676,12 +2666,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>approval_id</t>
+          <t>message_id + question_item_id</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>A-17 게이트. 한 번의 발송 승인 행위 그 자체 (L-11)</t>
+          <t>한 메시지에 여러 질문, 한 질문이 재발송으로 여러 메시지에</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2686,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>message_approval_structured_field</t>
+          <t>message_approval</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>승인 시점 구조화 값</t>
+          <t>메시지 승인</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2721,12 +2711,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>approval_id + field_key</t>
+          <t>approval_id</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>운영자가 승인한 그 숫자의 사본 (rev.2 신규)</t>
+          <t>A-17 게이트. 한 번의 발송 승인 행위 그 자체 (L-11)</t>
         </is>
       </c>
     </row>
@@ -2741,22 +2731,22 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>send_attempt</t>
+          <t>message_approval_structured_field</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>발송 시도</t>
+          <t>승인 시점 구조화 값</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>SOURCE_OF_TRUTH</t>
+          <t>DECISION_RECORD</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (결과 5컬럼)</t>
+          <t>APPEND_ONLY</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -2766,12 +2756,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>send_attempt_id</t>
+          <t>approval_id + field_key</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>실제 발송 1회 시도 (L-7)</t>
+          <t>운영자가 승인한 그 숫자의 사본 (rev.2 신규)</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2776,12 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>message_status_transition</t>
+          <t>send_attempt</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>메시지 상태 전이</t>
+          <t>발송 시도</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2801,7 +2791,7 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (결과 5컬럼)</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -2811,12 +2801,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>transition_id</t>
+          <t>send_attempt_id</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>메시지 상태가 바뀐 이력. 상태의 정본은 여기다</t>
+          <t>실제 발송 1회 시도 (L-7)</t>
         </is>
       </c>
     </row>
@@ -2831,22 +2821,22 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>message_status_transition</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>추출 기록</t>
+          <t>메시지 상태 전이</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>EVIDENCE</t>
+          <t>SOURCE_OF_TRUTH</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (검토 4컬럼)</t>
+          <t>APPEND_ONLY</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -2856,12 +2846,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>extraction_id</t>
+          <t>transition_id</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>LLM 추출 1회의 기록. 후보 값 + 원문 인용까지가 LLM 의 역할이다</t>
+          <t>메시지 상태가 바뀐 이력. 상태의 정본은 여기다</t>
         </is>
       </c>
     </row>
@@ -2871,27 +2861,27 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>09_감사운영</t>
+          <t>08_외부통신</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>actor</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>행위 주체</t>
+          <t>추출 기록</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>EVIDENCE</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>CONTROLLED_UPDATE</t>
+          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (검토 4컬럼)</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -2901,12 +2891,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>actor_id</t>
+          <t>extraction_id</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>CERA 안에서 행동한 주체. 최소 구성 (Q-62)</t>
+          <t>LLM 추출 1회의 기록. 후보 값 + 원문 인용까지가 LLM 의 역할이다</t>
         </is>
       </c>
     </row>
@@ -2921,22 +2911,22 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>audit_log</t>
+          <t>actor</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>감사 기록</t>
+          <t>행위 주체</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>SOURCE_OF_TRUTH</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>APPEND_ONLY</t>
+          <t>CONTROLLED_UPDATE</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -2946,12 +2936,12 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>audit_id</t>
+          <t>actor_id</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>되돌릴 수 없는 행위의 책임 추적. 현재 상태에 영향을 주지 않는다</t>
+          <t>CERA 안에서 행동한 주체. 최소 구성 (Q-62)</t>
         </is>
       </c>
     </row>
@@ -2966,17 +2956,17 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>system_error</t>
+          <t>audit_log</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>시스템·연동 오류 기록</t>
+          <t>감사 기록</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>EVIDENCE</t>
+          <t>SOURCE_OF_TRUTH</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -2986,17 +2976,17 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>MVP · rev.2.2</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>error_id</t>
+          <t>audit_id</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>중요한 시스템/외부 연동 오류를 DB 에서 찾기 위한 기술 운영 표. 업무 개념이 아니다 (docs/23)</t>
+          <t>되돌릴 수 없는 행위의 책임 추적. 현재 상태에 영향을 주지 않는다</t>
         </is>
       </c>
     </row>
@@ -3011,84 +3001,82 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
+          <t>system_error</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>시스템·연동 오류 기록</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>APPEND_ONLY</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>MVP · rev.2.2</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>error_id</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>중요한 시스템/외부 연동 오류를 DB 에서 찾기 위한 기술 운영 표. 업무 개념이 아니다 (docs/23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>09_감사운영</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>시나리오</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>SIMULATION_ONLY</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>CONTROLLED_UPDATE</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>재생 시나리오. 제품 도메인이 아니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>10_OpenDecisions</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>exception_case</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>예외 운영 Case</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>CLOSED FOR MVP - 만들지 않는다</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="12" t="inlineStr">
-        <is>
-          <t>Event -&gt; Risk -&gt; RecoveryRun -&gt; Communication -&gt; Reply -&gt; Re-run 폐쇄 루프에 필수가 아니다. 현재는 파생 조회  [E-36 · L-10 · D-5]</t>
         </is>
       </c>
     </row>
@@ -3105,131 +3093,178 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
+          <t>exception_case</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>예외 운영 Case</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>CLOSED FOR MVP - 만들지 않는다</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="12" t="inlineStr">
+        <is>
+          <t>Event -&gt; Risk -&gt; RecoveryRun -&gt; Communication -&gt; Reply -&gt; Re-run 폐쇄 루프에 필수가 아니다. 현재는 파생 조회  [E-36 · L-10 · D-5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>10_OpenDecisions</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
           <t>operational_plan_batch</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>계획 업로드 묶음</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>CLOSED - 만들지 않는다</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="12" t="inlineStr">
+      <c r="I66" s="12" t="inlineStr">
         <is>
           <t>raw_input 1행이 이미 업로드 1건이고 그 배치의 plan.* 사건이 같은 raw_input_id 를 공유한다  [E-35 · L-9 · D-4]</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>만들지 않은 것</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>이유</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>truck (개별 차량)</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>MVP 기능이 풀 + 슬롯별 가용량으로 성립한다 (E-39, Q-57)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>truck (개별 차량)</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>값 객체. cost_line_item 의 금액 컬럼 묶음 (Q-58)</t>
+          <t>MVP 기능이 풀 + 슬롯별 가용량으로 성립한다 (E-39, Q-57)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>phase / container_phase</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>파생. 원본으로 저장하지 않는다 (안티패턴 1)</t>
+          <t>값 객체. cost_line_item 의 금액 컬럼 묶음 (Q-58)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>slot_pool</t>
+          <t>phase / container_phase</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>터미널의 자원 단위. 슬롯 가용은 사실</t>
+          <t>파생. 원본으로 저장하지 않는다 (안티패턴 1)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>destination / carrier</t>
+          <t>slot_pool</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>관계에 붙은 역할. 별도 테이블 아님</t>
+          <t>터미널의 자원 단위. 슬롯 가용은 사실</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>activity_timeline</t>
+          <t>destination / carrier</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>다섯 원본을 합친 조회 뷰</t>
+          <t>관계에 붙은 역할. 별도 테이블 아님</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>activity_timeline</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>다섯 원본을 합친 조회 뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
           <t>code_group / code_value</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>코드 테이블은 물리 설계에서 형태를 정한다 (18절)</t>
         </is>
@@ -5074,7 +5109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5088,7 +5123,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>사용자 결정 결과 · 열린 질문 판정 (rev.2.2 최종 정리)</t>
+          <t>사용자 결정 결과 · 열린 질문 판정 (rev.2.3 T-081)</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5137,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>[1] 사용자 결정 (5건 - 2026-09-17 전부 CLOSED)</t>
+          <t>[1] 사용자 결정 (6건 - D-1~D-5 2026-09-17, C 2026-09-21 전부 CLOSED)</t>
         </is>
       </c>
     </row>
@@ -5298,653 +5333,663 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>출처 어휘를 무엇으로 통일할까 (docs/05 3.1 7값 vs rev.2.2 source_kind 6값)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>① ADR-020 의 3축·7값으로 맞춘다  ② 6값을 유지하고 ADR-020 을 개정한다  ③ Q-46 까지 함께 재설계한다</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>CLOSED - ① 3축 통일 (2026-09-21 사용자 결정)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ADR-020 은 Accepted (구조 한정). 6값으로는 docs/05 3.3 근거 강도표를 색인할 수 없어 Reconciliation 이 돌지 않는다. ③은 Q-46 이 사람 결정으로 열려 있어 이번 범위 밖</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>매우 어려움 - append-only 사건 행에 값이 박히고 강도표·권한 매트릭스가 이 값을 색인으로 쓴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[2] MVP 에서 만들지 않기로 한 테이블</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>영문 테이블명</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>한글</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>근거 항목</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>결정</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>근거</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>다시 여는 조건</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>exception_case</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>예외 운영 Case</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>E-36 · L-10 · D-5</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED FOR MVP - 만들지 않는다</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Event -&gt; Risk -&gt; RecoveryRun -&gt; Communication -&gt; Reply -&gt; Re-run 폐쇄 루프에 필수가 아니다. 현재는 파생 조회</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>다시 여는 조건: 담당자 배정 · 예외 건 상태 · 종결 · SLA · Case 단위 협업. 만들 때는 결정적 case_key</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>exception_case</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>예외 운영 Case</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>E-36 · L-10 · D-5</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>CLOSED FOR MVP - 만들지 않는다</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Event -&gt; Risk -&gt; RecoveryRun -&gt; Communication -&gt; Reply -&gt; Re-run 폐쇄 루프에 필수가 아니다. 현재는 파생 조회</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>다시 여는 조건: 담당자 배정 · 예외 건 상태 · 종결 · SLA · Case 단위 협업. 만들 때는 결정적 case_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>operational_plan_batch</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>계획 업로드 묶음</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>E-35 · L-9 · D-4</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>CLOSED - 만들지 않는다</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>raw_input 1행이 이미 업로드 1건이고 그 배치의 plan.* 사건이 같은 raw_input_id 를 공유한다</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>다시 여는 조건: 배치 이름 · 상태 · 버전 · 승인 · 묶음 단위 되돌리기/교체</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>[3] 이번 단계에서 판정한 열린 질문</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>질문</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>스키마 반영</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>Q-54</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>외부 시스템 식별자 저장 구조</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>하이브리드</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>조회 경로 id 는 컬럼(comm_message/comm_thread), 화물·통관 id 는 external_identifier</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>Q-55</t>
+          <t>Q-54</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>시설 하위 종류 구조</t>
+          <t>외부 시스템 식별자 저장 구조</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>공통 + 1:1 상세</t>
+          <t>하이브리드</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>facility + facility_warehouse / facility_terminal / facility_odcy</t>
+          <t>조회 경로 id 는 컬럼(comm_message/comm_thread), 화물·통관 id 는 external_identifier</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>Q-58</t>
+          <t>Q-55</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>금액·통화 표현</t>
+          <t>시설 하위 종류 구조</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>컬럼 묶음</t>
+          <t>공통 + 1:1 상세</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Money 테이블 없음. amount_krw + original_currency/amount + fx_rate + fx_rate_basis_date</t>
+          <t>facility + facility_warehouse / facility_terminal / facility_odcy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>Q-59</t>
+          <t>Q-58</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>확인 요청 처리 기록의 참조 대상</t>
+          <t>금액·통화 표현</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>결정적 request_key (DB FK 아님)</t>
+          <t>컬럼 묶음</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>rev.2: DB 외래키가 아니라 논리 연결 키. 재료에서 conflict_id 같은 파생 대리키 제거</t>
+          <t>Money 테이블 없음. amount_krw + original_currency/amount + fx_rate + fx_rate_basis_date</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>Q-60</t>
+          <t>Q-59</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>CostLineItem 의 귀속</t>
+          <t>확인 요청 처리 기록의 참조 대상</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>필수 부모 1개 + 링크 테이블</t>
+          <t>결정적 request_key (DB FK 아님)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>cost_result_id 만 NOT NULL. 귀속·근거는 cost_line_link(link_role)</t>
+          <t>rev.2: DB 외래키가 아니라 논리 연결 키. 재료에서 conflict_id 같은 파생 대리키 제거</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>Q-62</t>
+          <t>Q-60</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Actor 구조</t>
+          <t>CostLineItem 의 귀속</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>최소 구성</t>
+          <t>필수 부모 1개 + 링크 테이블</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>actor_id / actor_type / display_name / is_active. 인증·권한은 나중</t>
+          <t>cost_result_id 만 NOT NULL. 귀속·근거는 cost_line_link(link_role)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>Q-63</t>
+          <t>Q-62</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>fact_key 분해</t>
+          <t>Actor 구조</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>원본은 문자열 유지</t>
+          <t>최소 구성</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>event.fact_key 는 불변 문자열. 파생 canonical_fact 에만 param_* 분해 컬럼</t>
+          <t>actor_id / actor_type / display_name / is_active. 인증·권한은 나중</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>L-1</t>
+          <t>Q-63</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>회신 값을 원래 질문에 되붙이기</t>
+          <t>fact_key 분해</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>질문 생성 시 대상 확정</t>
+          <t>원본은 문자열 유지</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>question_item 이 target_entity_type/id · target_fact_key · target_applicability_scope_type/ref(rev.2.1) 를 질문 생성 시 확정하고 ask_id 로 단건 조회. 개체·사실 키·적용 범위가 모두 그 행에서 나오며 LLM 은 범위를 만지지 않는다</t>
+          <t>event.fact_key 는 불변 문자열. 파생 canonical_fact 에만 param_* 분해 컬럼</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>L-2</t>
+          <t>L-1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Container ↔ B/L</t>
+          <t>회신 값을 원래 질문에 되붙이기</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>연결 테이블</t>
+          <t>질문 생성 시 대상 확정</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>container_bl + PRIMARY 부분 유일 제약 (D-1 CLOSED)</t>
+          <t>question_item 이 target_entity_type/id · target_fact_key · target_applicability_scope_type/ref(rev.2.1) 를 질문 생성 시 확정하고 ask_id 로 단건 조회. 개체·사실 키·적용 범위가 모두 그 행에서 나오며 LLM 은 범위를 만지지 않는다</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>L-3</t>
+          <t>L-2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>제안 묶음</t>
+          <t>Container ↔ B/L</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>테이블로 만든다</t>
+          <t>연결 테이블</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>commercial_offer + item, 분류 EVIDENCE (D-2 CLOSED)</t>
+          <t>container_bl + PRIMARY 부분 유일 제약 (D-1 CLOSED)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>L-3b</t>
+          <t>L-3</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>운영자 입력 요율의 적용 대상·기간</t>
+          <t>제안 묶음</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>범위와 기간을 분리</t>
+          <t>테이블로 만든다</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>rev.2: valid_from/until(시간) 과 applicability_scope_type/ref(대상) 을 다른 축으로. 기본 RECOVERY_CONTEXT</t>
+          <t>commercial_offer + item, 분류 EVIDENCE (D-2 CLOSED)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>L-4</t>
+          <t>L-3b</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>마스터 값 vs 사실</t>
+          <t>운영자 입력 요율의 적용 대상·기간</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>default_ 접두</t>
+          <t>범위와 기간을 분리</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>마스터에는 평시 기준선만. 그날 값은 사실이 이긴다. 계산에 쓴 기본값은 스냅샷에 얼린다</t>
+          <t>rev.2: valid_from/until(시간) 과 applicability_scope_type/ref(대상) 을 다른 축으로. 기본 RECOVERY_CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>L-5</t>
+          <t>L-4</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>차량 표현</t>
+          <t>마스터 값 vs 사실</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>풀 단위</t>
+          <t>default_ 접두</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>plan.truck_pool / plan.depart_slot 사실. 개별 차량 없음</t>
+          <t>마스터에는 평시 기준선만. 그날 값은 사실이 이긴다. 계산에 쓴 기본값은 스냅샷에 얼린다</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>L-6</t>
+          <t>L-5</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>예외 처리 단위</t>
+          <t>차량 표현</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>L-10 으로 합침</t>
+          <t>풀 단위</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>D-5 CLOSED FOR MVP</t>
+          <t>plan.truck_pool / plan.depart_slot 사실. 개별 차량 없음</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>L-7</t>
+          <t>L-6</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>발송 시도</t>
+          <t>예외 처리 단위</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>별도 테이블</t>
+          <t>L-10 으로 합침</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>send_attempt. rev.2: 승인은 메시지 종류에 따른 조건부 필수</t>
+          <t>D-5 CLOSED FOR MVP</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>L-8</t>
+          <t>L-7</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>시뮬레이션 분리</t>
+          <t>발송 시도</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>같은 테이블 + 플래그</t>
+          <t>별도 테이블</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>is_simulated + scenario_id, 산출물은 contains_simulated 로 전파</t>
+          <t>send_attempt. rev.2: 승인은 메시지 종류에 따른 조건부 필수</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>L-9</t>
+          <t>L-8</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>계획 업로드 묶음</t>
+          <t>시뮬레이션 분리</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>만들지 않는다</t>
+          <t>같은 테이블 + 플래그</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>raw_input 이 배치 출처 (D-4 CLOSED)</t>
+          <t>is_simulated + scenario_id, 산출물은 contains_simulated 로 전파</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-9</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ExceptionCase</t>
+          <t>계획 업로드 묶음</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>MVP 에서 만들지 않는다</t>
+          <t>만들지 않는다</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>파생 조회 (D-5 CLOSED FOR MVP)</t>
+          <t>raw_input 이 배치 출처 (D-4 CLOSED)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MessageApproval</t>
+          <t>ExceptionCase</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>덧붙이기 + 승인 사본 + 무효화 행</t>
+          <t>MVP 에서 만들지 않는다</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>rev.2: 구조화 값까지 얼리고, 취소·만료·계획 교체를 UPDATE 없이 남긴다</t>
+          <t>파생 조회 (D-5 CLOSED FOR MVP)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>운영자 계획 조건</t>
+          <t>MessageApproval</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>별도 DECISION_RECORD 테이블</t>
+          <t>덧붙이기 + 승인 사본 + 무효화 행</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>rev.2: 해제도 action=RELEASE 새 행. 기본 범위는 RECOVERY_CONTEXT. 솔버 표현은 미확정</t>
+          <t>rev.2: 구조화 값까지 얼리고, 취소·만료·계획 교체를 UPDATE 없이 남긴다</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>L-13</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>복구 맥락(Recovery Context)의 식별자</t>
+          <t>운영자 계획 조건</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>OPEN - rev.2 신규</t>
+          <t>별도 DECISION_RECORD 테이블</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>후보: recovery_run 계보의 뿌리 / 최초 계기 사건 / 컨테이너 집합 지문. T-069 에서 답한다</t>
+          <t>rev.2: 해제도 action=RELEASE 새 행. 기본 범위는 RECOVERY_CONTEXT. 솔버 표현은 미확정</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>L-14</t>
+          <t>L-13</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>적용 범위의 값 목록 + 범위 선택 정책</t>
+          <t>복구 맥락(Recovery Context)의 식별자</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>OPEN - rev.2 신규 / rev.2.1 확장</t>
+          <t>OPEN - rev.2 신규</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>① 값 목록 enum 미확정 (기본값이 RECOVERY_CONTEXT 라는 것만 확정) ② 여러 범위가 동시에 적용 가능할 때의 선택 정책도 확정하지 않는다 - CONTRACT/CONTAINER/RECOVERY_CONTEXT 는 서로 다른 축이라 한 줄로 못 세운다. 확정한 것: 범위는 사실 식별자에 포함 · 같은 범위끼리만 Reconciliation · 결정론적 선택 정책이 필요함 · 쓴 범위는 스냅샷에 남음</t>
+          <t>후보: recovery_run 계보의 뿌리 / 최초 계기 사건 / 컨테이너 집합 지문. T-069 에서 답한다</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>L-15</t>
+          <t>L-14</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>message_kind 값 목록</t>
+          <t>적용 범위의 값 목록 + 범위 선택 정책</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>OPEN - rev.2 신규</t>
+          <t>OPEN - rev.2 신규 / rev.2.1 확장</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>지금은 BUSINESS / CONTACT_VERIFICATION 둘만. 늘리는 것은 쉽다</t>
+          <t>① 값 목록 enum 미확정 (기본값이 RECOVERY_CONTEXT 라는 것만 확정) ② 여러 범위가 동시에 적용 가능할 때의 선택 정책도 확정하지 않는다 - CONTRACT/CONTAINER/RECOVERY_CONTEXT 는 서로 다른 축이라 한 줄로 못 세운다. 확정한 것: 범위는 사실 식별자에 포함 · 같은 범위끼리만 Reconciliation · 결정론적 선택 정책이 필요함 · 쓴 범위는 스냅샷에 남음</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>L-16</t>
+          <t>L-15</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>bl 의 업무 유일 제약</t>
+          <t>message_kind 값 목록</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -5954,141 +5999,228 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>(bl_type, bl_no, bl_year) 는 후보일 뿐. 번호가 연도 안에서 유일한지 미확인. 실데이터 확인 뒤 물리 설계</t>
+          <t>지금은 BUSINESS / CONTACT_VERIFICATION 둘만. 늘리는 것은 쉽다</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
+          <t>L-16</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>bl 의 업무 유일 제약</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>OPEN - rev.2 신규</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>(bl_type, bl_no, bl_year) 는 후보일 뿐. 번호가 연도 안에서 유일한지 미확인. 실데이터 확인 뒤 물리 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
           <t>Q-66</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>system_error 의 오류 분류·코드 값 목록</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>OPEN - rev.2.2 신규</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>예시(GMAIL_TIMEOUT · GMAIL_RATE_LIMITED · GMAIL_AUTH_EXPIRED · EXTERNAL_RESPONSE_INVALID)만 적었다. 전체 목록은 T-069 구현 계획·구현에서 정한다 (docs/23 6절)</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Q-46</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>상대방이 직접 입력한 구조화 값의 Source 모델</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OPEN - 유지 (rev.2.3 에서 닫지 않았다)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>source_type 7값은 현재 ADR-020 기준의 정렬이지 영구 확정 enum 이 아니다. HUMAN_UI 로 넣으면 거래처 입력이 CERA 사용자 입력과 같은 강도가 되어 권한 모델이 무너진다. actor_type 축 신설 여부는 권한 모델과 함께 정한다</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Q-34</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>event.payload.change_reason 의 값 목록</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OPEN - rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>R6 변화 선언 예외 판정의 입력. 값 목록은 T-037 · 인터뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>[4] 이번 단계에서 정하지 않는 것</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>DB 제품 (PostgreSQL / MySQL / SQLite)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>실제 CREATE TABLE SQL / 마이그레이션</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>인덱스·파티션·복제</t>
+          <t>DB 제품 (PostgreSQL / MySQL / SQLite)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>API endpoint</t>
+          <t>ORM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>LLM 공급자·모델</t>
+          <t>실제 CREATE TABLE SQL / 마이그레이션</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>솔버와 그 내부 표현</t>
+          <t>인덱스·파티션·복제</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>위험·신선도·근거 강도의 실제 임계값</t>
+          <t>API endpoint</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>plan_decision.decision_type 의 값 목록</t>
+          <t>LLM 공급자·모델</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>applicability_scope_type 값 목록 (L-14)</t>
+          <t>솔버와 그 내부 표현</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>복구 맥락 식별자 (L-13)</t>
+          <t>위험·신선도·근거 강도의 실제 임계값</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>bl 의 실제 UNIQUE 제약 (L-16)</t>
+          <t>plan_decision.decision_type 의 값 목록</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>적용 범위 사이의 우선순위 규칙 (L-14)</t>
+          <t>applicability_scope_type 값 목록 (L-14)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>system_error 오류 분류·코드 값 목록 (Q-66)</t>
+          <t>복구 맥락 식별자 (L-13)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
+          <t>bl 의 실제 UNIQUE 제약 (L-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>적용 범위 사이의 우선순위 규칙 (L-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>system_error 오류 분류·코드 값 목록 (Q-66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
           <t>Backend 언어·프레임워크 (ADR-031 Proposed, docs/23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>event.idempotency_key 의 직렬화·해시 알고리즘·주장 위치(claim locator) 형식 (11.2d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>event.schema_version 문자열 형식</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>input_confidence_reasons / validator_result 의 JSON 구조 세부</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH79"/>
+  <dimension ref="A1:AN89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11271,7 +11403,7 @@
           <t>영문 테이블명</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>raw_input</t>
         </is>
@@ -11281,7 +11413,7 @@
           <t>한글 테이블명</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>원천 입력</t>
         </is>
@@ -11291,7 +11423,7 @@
           <t>분류</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>SOURCE_OF_TRUTH</t>
         </is>
@@ -11301,7 +11433,7 @@
           <t>단계</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -11311,7 +11443,7 @@
           <t>변경 방식</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>APPEND_ONLY</t>
         </is>
@@ -11337,7 +11469,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>rev.2: payload_hash UNIQUE 제거. 내용이 같아도 재수집은 새 관측이다 (예시 1·2 는 같은 해시). 중복 처리 차단은 출처가 주는 source_record_key 로만 한다</t>
+          <t>rev.2: payload_hash UNIQUE 제거. 내용이 같아도 재수집은 새 관측이다 (예시 1·2 는 같은 해시). 중복 처리 차단은 출처가 주는 source_record_key 로만 한다 / rev.2.3: source_type 값을 ADR-020 7값으로 맞췄다 (event.source_type 과 같은 집합)</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11486,7 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>출처 종류</t>
+          <t>출처 종류(채널)</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
@@ -11414,52 +11546,52 @@
           <t>raw_input_id</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>source_type</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>source_name</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>request_ref</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>payload_ref</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>payload_hash</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>source_record_key</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>source_recorded_at</t>
         </is>
       </c>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>received_at</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>collected_by_actor_id</t>
         </is>
       </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>is_simulated</t>
         </is>
@@ -11540,7 +11672,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>PUBLIC_API / EMAIL / DOCUMENT / HUMAN_INPUT / PLAN_UPLOAD / INTERNAL</t>
+          <t>NOT NULL / HUMAN_UI / FILE_IMPORT / EMAIL / DOCUMENT / PUBLIC_API / PARTNER_SYSTEM / INFERENCE / rev.2.3 값 변경</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -11625,7 +11757,7 @@
           <t>(해시값)</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T06:00+09:00</t>
@@ -11683,7 +11815,7 @@
           <t>(같은 해시값)</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T10:00+09:00</t>
@@ -11726,7 +11858,7 @@
           <t>MOCK_INBOX</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>store://raw/000009</t>
@@ -11772,7 +11904,7 @@
           <t>영문 테이블명</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>event</t>
         </is>
@@ -11782,7 +11914,7 @@
           <t>한글 테이블명</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>사건</t>
         </is>
@@ -11792,7 +11924,7 @@
           <t>분류</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>SOURCE_OF_TRUTH</t>
         </is>
@@ -11802,7 +11934,7 @@
           <t>단계</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -11812,7 +11944,7 @@
           <t>변경 방식</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>APPEND_ONLY</t>
         </is>
@@ -11826,7 +11958,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>사실 주장 한 건. Append-only. UPDATE / DELETE 금지</t>
+          <t>사실 주장 한 건. Append-only. UPDATE / DELETE 없음</t>
         </is>
       </c>
     </row>
@@ -11838,7 +11970,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>rev.2: source_tier 제거(근거 강도는 계산 결과 -&gt; canonical_fact). 원천 축만 남긴다. 적용 범위(scope)와 유효 기간(validity)은 다른 축이다. 예시 3 = 운영자의 '이번 건만 0원' / rev.2.2: 복구 맥락 참조는 자리표시자 &lt;RECOVERY_CONTEXT_REF&gt; 로 적는다 - 별도 RecoveryContext 표도, recovery_run id 라는 뜻도 아니다. 식별 방식은 L-13 이 정한다</t>
+          <t>rev.2: source_tier 제거(근거 강도는 계산 결과 -&gt; canonical_fact). 원천 축만 남긴다. 적용 범위(scope)와 유효 기간(validity)은 다른 축이다. 예시 3 = 운영자의 '이번 건만 0원' / rev.2.2: 복구 맥락 참조는 자리표시자 &lt;RECOVERY_CONTEXT_REF&gt; 로 적는다 - 별도 RecoveryContext 표도, recovery_run id 라는 뜻도 아니다. 식별 방식은 L-13 이 정한다 / rev.2.3: docs/05 4.2 와 한 줄씩 대조해 13개 누락을 복구했다 (event_class · event_type · schema_version · verification 2필드 · idempotency_key · correlation_id · payload · source_id · extraction_method · 검증기 신뢰도 2필드 · source_type 값). 대응표는 Markdown 23.1</t>
         </is>
       </c>
     </row>
@@ -11855,130 +11987,190 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
+          <t>스키마 판</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
           <t>원천 입력</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>사건 부류</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>업무 사건 유형</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>사실 종류</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>사실 키</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>값(문자)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>값(수치)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="K22" s="16" t="inlineStr">
         <is>
           <t>값(시각)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="L22" s="16" t="inlineStr">
         <is>
           <t>값(코드)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="M22" s="16" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="N22" s="16" t="inlineStr">
         <is>
           <t>적용 시작</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="O22" s="16" t="inlineStr">
         <is>
           <t>적용 종료</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr">
+      <c r="P22" s="16" t="inlineStr">
         <is>
           <t>적용 범위 종류</t>
         </is>
       </c>
-      <c r="N22" s="16" t="inlineStr">
+      <c r="Q22" s="16" t="inlineStr">
         <is>
           <t>적용 범위 참조</t>
         </is>
       </c>
-      <c r="O22" s="16" t="inlineStr">
+      <c r="R22" s="16" t="inlineStr">
         <is>
           <t>관측 시각</t>
         </is>
       </c>
-      <c r="P22" s="16" t="inlineStr">
+      <c r="S22" s="16" t="inlineStr">
         <is>
           <t>출처 기록 시각</t>
         </is>
       </c>
-      <c r="Q22" s="16" t="inlineStr">
+      <c r="T22" s="16" t="inlineStr">
         <is>
           <t>수신 시각</t>
         </is>
       </c>
-      <c r="R22" s="16" t="inlineStr">
-        <is>
-          <t>출처 종류</t>
-        </is>
-      </c>
-      <c r="S22" s="16" t="inlineStr">
+      <c r="U22" s="16" t="inlineStr">
+        <is>
+          <t>출처 종류(채널)</t>
+        </is>
+      </c>
+      <c r="V22" s="16" t="inlineStr">
         <is>
           <t>수집 시점 역할</t>
         </is>
       </c>
-      <c r="T22" s="16" t="inlineStr">
+      <c r="W22" s="16" t="inlineStr">
+        <is>
+          <t>출처 주체</t>
+        </is>
+      </c>
+      <c r="X22" s="16" t="inlineStr">
+        <is>
+          <t>추출 방식</t>
+        </is>
+      </c>
+      <c r="Y22" s="16" t="inlineStr">
         <is>
           <t>입력 품질</t>
         </is>
       </c>
-      <c r="U22" s="16" t="inlineStr">
+      <c r="Z22" s="16" t="inlineStr">
+        <is>
+          <t>검증기 신뢰도</t>
+        </is>
+      </c>
+      <c r="AA22" s="16" t="inlineStr">
+        <is>
+          <t>신뢰도 사유</t>
+        </is>
+      </c>
+      <c r="AB22" s="16" t="inlineStr">
         <is>
           <t>신뢰 주체</t>
         </is>
       </c>
-      <c r="V22" s="16" t="inlineStr">
+      <c r="AC22" s="16" t="inlineStr">
         <is>
           <t>입력 주체</t>
         </is>
       </c>
-      <c r="W22" s="16" t="inlineStr">
+      <c r="AD22" s="16" t="inlineStr">
         <is>
           <t>정정 대상</t>
         </is>
       </c>
-      <c r="X22" s="16" t="inlineStr">
+      <c r="AE22" s="16" t="inlineStr">
         <is>
           <t>정정 사유</t>
         </is>
       </c>
-      <c r="Y22" s="16" t="inlineStr">
+      <c r="AF22" s="16" t="inlineStr">
+        <is>
+          <t>확인 행위</t>
+        </is>
+      </c>
+      <c r="AG22" s="16" t="inlineStr">
+        <is>
+          <t>확인 방법</t>
+        </is>
+      </c>
+      <c r="AH22" s="16" t="inlineStr">
         <is>
           <t>추출 근거</t>
         </is>
       </c>
-      <c r="Z22" s="16" t="inlineStr">
+      <c r="AI22" s="16" t="inlineStr">
+        <is>
+          <t>업무 상관 id</t>
+        </is>
+      </c>
+      <c r="AJ22" s="16" t="inlineStr">
+        <is>
+          <t>멱등 키</t>
+        </is>
+      </c>
+      <c r="AK22" s="16" t="inlineStr">
+        <is>
+          <t>부가 속성</t>
+        </is>
+      </c>
+      <c r="AL22" s="16" t="inlineStr">
         <is>
           <t>기록 시각</t>
         </is>
       </c>
-      <c r="AA22" s="16" t="inlineStr">
+      <c r="AM22" s="16" t="inlineStr">
         <is>
           <t>시뮬레이션</t>
         </is>
       </c>
-      <c r="AB22" s="16" t="inlineStr">
+      <c r="AN22" s="16" t="inlineStr">
         <is>
           <t>시나리오</t>
         </is>
@@ -11995,132 +12187,192 @@
           <t>event_id</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>raw_input_id</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>event_class</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>fact_kind</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>fact_key</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>value_text</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>value_number</t>
         </is>
       </c>
-      <c r="H23" s="19" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>value_timestamp</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>value_code</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="M23" s="17" t="inlineStr">
         <is>
           <t>value_unit</t>
         </is>
       </c>
-      <c r="K23" s="19" t="inlineStr">
+      <c r="N23" s="17" t="inlineStr">
         <is>
           <t>valid_from</t>
         </is>
       </c>
-      <c r="L23" s="19" t="inlineStr">
+      <c r="O23" s="17" t="inlineStr">
         <is>
           <t>valid_until</t>
         </is>
       </c>
-      <c r="M23" s="19" t="inlineStr">
+      <c r="P23" s="17" t="inlineStr">
         <is>
           <t>applicability_scope_type</t>
         </is>
       </c>
-      <c r="N23" s="19" t="inlineStr">
+      <c r="Q23" s="17" t="inlineStr">
         <is>
           <t>applicability_scope_ref</t>
         </is>
       </c>
-      <c r="O23" s="19" t="inlineStr">
+      <c r="R23" s="17" t="inlineStr">
         <is>
           <t>source_event_time</t>
         </is>
       </c>
-      <c r="P23" s="19" t="inlineStr">
+      <c r="S23" s="17" t="inlineStr">
         <is>
           <t>source_recorded_at</t>
         </is>
       </c>
-      <c r="Q23" s="19" t="inlineStr">
+      <c r="T23" s="17" t="inlineStr">
         <is>
           <t>received_at</t>
         </is>
       </c>
-      <c r="R23" s="19" t="inlineStr">
-        <is>
-          <t>source_kind</t>
-        </is>
-      </c>
-      <c r="S23" s="19" t="inlineStr">
+      <c r="U23" s="17" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="V23" s="17" t="inlineStr">
         <is>
           <t>source_role_at_ingestion</t>
         </is>
       </c>
-      <c r="T23" s="19" t="inlineStr">
+      <c r="W23" s="17" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="X23" s="17" t="inlineStr">
+        <is>
+          <t>extraction_method</t>
+        </is>
+      </c>
+      <c r="Y23" s="17" t="inlineStr">
         <is>
           <t>input_quality</t>
         </is>
       </c>
-      <c r="U23" s="20" t="inlineStr">
+      <c r="Z23" s="17" t="inlineStr">
+        <is>
+          <t>input_confidence_level</t>
+        </is>
+      </c>
+      <c r="AA23" s="17" t="inlineStr">
+        <is>
+          <t>input_confidence_reasons</t>
+        </is>
+      </c>
+      <c r="AB23" s="20" t="inlineStr">
         <is>
           <t>asserted_by_counterparty_id</t>
         </is>
       </c>
-      <c r="V23" s="20" t="inlineStr">
+      <c r="AC23" s="20" t="inlineStr">
         <is>
           <t>entered_by_actor_id</t>
         </is>
       </c>
-      <c r="W23" s="20" t="inlineStr">
+      <c r="AD23" s="20" t="inlineStr">
         <is>
           <t>supersedes_event_id</t>
         </is>
       </c>
-      <c r="X23" s="19" t="inlineStr">
+      <c r="AE23" s="17" t="inlineStr">
         <is>
           <t>supersede_reason</t>
         </is>
       </c>
-      <c r="Y23" s="20" t="inlineStr">
+      <c r="AF23" s="17" t="inlineStr">
+        <is>
+          <t>verification_action</t>
+        </is>
+      </c>
+      <c r="AG23" s="17" t="inlineStr">
+        <is>
+          <t>verification_method</t>
+        </is>
+      </c>
+      <c r="AH23" s="20" t="inlineStr">
         <is>
           <t>extraction_id</t>
         </is>
       </c>
-      <c r="Z23" s="19" t="inlineStr">
+      <c r="AI23" s="17" t="inlineStr">
+        <is>
+          <t>correlation_id</t>
+        </is>
+      </c>
+      <c r="AJ23" s="18" t="inlineStr">
+        <is>
+          <t>idempotency_key</t>
+        </is>
+      </c>
+      <c r="AK23" s="17" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="AL23" s="17" t="inlineStr">
         <is>
           <t>recorded_at</t>
         </is>
       </c>
-      <c r="AA23" s="19" t="inlineStr">
+      <c r="AM23" s="17" t="inlineStr">
         <is>
           <t>is_simulated</t>
         </is>
       </c>
-      <c r="AB23" s="20" t="inlineStr">
+      <c r="AN23" s="20" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
@@ -12139,130 +12391,190 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
+          <t>STRING(20)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
           <t>REF(raw_input)</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>STRING(120)</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>TEXT</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>DECIMAL(18,4)</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="O24" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="N24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>STRING(60)</t>
         </is>
       </c>
-      <c r="O24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
+      <c r="S24" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="T24" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="U24" s="6" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="S24" s="6" t="inlineStr">
+      <c r="V24" s="6" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="T24" s="6" t="inlineStr">
+      <c r="W24" s="6" t="inlineStr">
+        <is>
+          <t>STRING(60)</t>
+        </is>
+      </c>
+      <c r="X24" s="6" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="U24" s="6" t="inlineStr">
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="Z24" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AA24" s="6" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="inlineStr">
         <is>
           <t>REF(counterparty)</t>
         </is>
       </c>
-      <c r="V24" s="6" t="inlineStr">
+      <c r="AC24" s="6" t="inlineStr">
         <is>
           <t>REF(actor)</t>
         </is>
       </c>
-      <c r="W24" s="6" t="inlineStr">
+      <c r="AD24" s="6" t="inlineStr">
         <is>
           <t>REF(event)</t>
         </is>
       </c>
-      <c r="X24" s="6" t="inlineStr">
+      <c r="AE24" s="6" t="inlineStr">
         <is>
           <t>STRING(200)</t>
         </is>
       </c>
-      <c r="Y24" s="6" t="inlineStr">
+      <c r="AF24" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AG24" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AH24" s="6" t="inlineStr">
         <is>
           <t>REF(extraction)</t>
         </is>
       </c>
-      <c r="Z24" s="6" t="inlineStr">
+      <c r="AI24" s="6" t="inlineStr">
+        <is>
+          <t>STRING(60)</t>
+        </is>
+      </c>
+      <c r="AJ24" s="6" t="inlineStr">
+        <is>
+          <t>HASH</t>
+        </is>
+      </c>
+      <c r="AK24" s="6" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="AL24" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
+      <c r="AM24" s="6" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="AB24" s="6" t="inlineStr">
+      <c r="AN24" s="6" t="inlineStr">
         <is>
           <t>REF(scenario)</t>
         </is>
@@ -12281,132 +12593,192 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
+          <t>NOT NULL / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>MILESTONE / STATE / OFFER / TERM / IDENTITY / PLAN / FORECAST</t>
-        </is>
-      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL / 불변 문자열</t>
+          <t>NOT NULL / OBSERVATION / CORRECTION / VERIFICATION / rev.2.3 신규</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>4종 중 최소 1개 필수</t>
+          <t>NOT NULL / docs/05 4.4 카탈로그 / rev.2.3 신규</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
+          <t>조건부 - VERIFICATION 이면 비움 / MILESTONE / STATE / OFFER / TERM / IDENTITY / PLAN / FORECAST</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>조건부 - VERIFICATION 이면 비움 / 불변 문자열</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVATION 이면 4종 중 최소 1개 / VERIFICATION 은 비움</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용 / 시간 범위</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용 / 시간 범위</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>NOT NULL / 기본 GLOBAL</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>NOT NULL / GLOBAL 이면 빈 문자열</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr">
+      <c r="S25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="Q25" s="3" t="inlineStr">
+      <c r="T25" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 원천 축</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 당시 역할</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>STRUCTURED / SEMI_STRUCTURED / UNSTRUCTURED</t>
-        </is>
-      </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
+          <t>NOT NULL / HUMAN_UI / FILE_IMPORT / EMAIL / DOCUMENT / PUBLIC_API / PARTNER_SYSTEM / INFERENCE / rev.2.3 값 변경</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 등록부가 결정론으로 정한다</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 채널 안의 안정 식별자 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / DIRECT / RULE_PARSED / LLM_EXTRACTED / CALCULATED / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / STRUCTURED / SEMI_STRUCTURED / UNSTRUCTURED</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / HIGH / MEDIUM / LOW / 결정론 검증기가 정한다 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 검사별 감점 사유 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="V25" s="3" t="inlineStr">
+      <c r="AC25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 자기참조 / 순환 금지</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
+      <c r="AD25" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTION 이면 필수 / 자기참조 / 순환 금지</t>
+        </is>
+      </c>
+      <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>VERIFICATION 이면 필수 / CONFIRM / REJECT / REVOKE / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>VERIFICATION 이면 필수 / DIRECT_REVIEW / REQUEST_RESOLUTION / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / LLM_EXTRACTED 이면 필수 (I-23)</t>
+        </is>
+      </c>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / trace_id 와 다른 것 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / UNIQUE / 재료는 11.2d / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 부가 속성만 / 핵심 구조를 넣지 않는다 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AL25" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="AA25" s="3" t="inlineStr">
+      <c r="AM25" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="AB25" s="3" t="inlineStr">
-        <is>
-          <t>is_simulated=true 일 때만</t>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / is_simulated = true 일 때만</t>
         </is>
       </c>
     </row>
@@ -12423,82 +12795,118 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
+          <t>ev-1</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
           <t>RIN-000001</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>DISCHARGED</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>MILESTONE</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>discharge.actual</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T05:40+09:00</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="Q26" s="3" t="n"/>
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T05:40+09:00</t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T06:00+09:00</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="inlineStr">
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>PUBLIC_API</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>PORT_SYSTEM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>DS-01</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>RULE_PARSED</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>STRUCTURED</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="n"/>
+      <c r="AB26" s="3" t="n"/>
+      <c r="AC26" s="3" t="n"/>
+      <c r="AD26" s="3" t="n"/>
+      <c r="AE26" s="3" t="n"/>
+      <c r="AF26" s="3" t="n"/>
+      <c r="AG26" s="3" t="n"/>
+      <c r="AH26" s="3" t="n"/>
+      <c r="AI26" s="3" t="n"/>
+      <c r="AJ26" s="3" t="inlineStr">
+        <is>
+          <t>(결정적 해시)</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="n"/>
+      <c r="AL26" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T06:00+09:00</t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>PUBLIC_API</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t>STRUCTURED</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr"/>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t>ACT-SYS-01</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr"/>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T06:00+09:00</t>
-        </is>
-      </c>
-      <c r="AA26" s="3" t="inlineStr">
+      <c r="AM26" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AB26" s="3" t="inlineStr"/>
+      <c r="AN26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
@@ -12513,98 +12921,154 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
+          <t>ev-1</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
           <t>RIN-000009</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>WAREHOUSE_CAPACITY_CHANGED</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>STATE</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>warehouse.capacity@2026-09-18</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>TEU</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T00:00+09:00</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T23:59+09:00</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T08:20+09:00</t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T08:25+09:00</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T10:30+09:00</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T10:31+09:00</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="V27" s="3" t="inlineStr">
         <is>
           <t>WAREHOUSE</t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>SND-WH01-01</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>LLM_EXTRACTED</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>UNSTRUCTURED</t>
         </is>
       </c>
-      <c r="U27" s="3" t="inlineStr">
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>[QUOTE_MATCHED, UNIT_EXPLICIT]</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
         <is>
           <t>CP-WH-01</t>
         </is>
       </c>
-      <c r="V27" s="3" t="inlineStr"/>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>EXT-0003</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T08:25+09:00</t>
-        </is>
-      </c>
-      <c r="AA27" s="3" t="inlineStr">
+      <c r="AC27" s="3" t="n"/>
+      <c r="AD27" s="3" t="n"/>
+      <c r="AE27" s="3" t="n"/>
+      <c r="AF27" s="3" t="n"/>
+      <c r="AG27" s="3" t="n"/>
+      <c r="AH27" s="3" t="inlineStr">
+        <is>
+          <t>EXT-0004</t>
+        </is>
+      </c>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>THR-0001</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr">
+        <is>
+          <t>(결정적 해시)</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>{change_reason: CAPACITY_REDUCED}</t>
+        </is>
+      </c>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T10:31+09:00</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AB27" s="3" t="inlineStr"/>
+      <c r="AN27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
@@ -12614,95 +13078,123 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>EVT-000077</t>
+          <t>EVT-000120</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>RIN-000015</t>
+          <t>ev-1</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>TERM</t>
+          <t>RIN-000021</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>warehouse.storage_rate</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T00:00+09:00</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>RECOVERY_CONTEXT</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:00+09:00</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:00+09:00</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>HUMAN_INPUT</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr"/>
+          <t>VERIFICATION</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>VERIFICATION_RECORDED</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="n"/>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="3" t="n"/>
       <c r="T28" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18T11:40+09:00</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>HUMAN_UI</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>OPERATOR</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>ACT-USR-01</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
           <t>STRUCTURED</t>
         </is>
       </c>
-      <c r="U28" s="3" t="inlineStr"/>
-      <c r="V28" s="3" t="inlineStr">
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="n"/>
+      <c r="AB28" s="3" t="n"/>
+      <c r="AC28" s="3" t="inlineStr">
         <is>
           <t>ACT-USR-01</t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:00+09:00</t>
-        </is>
-      </c>
-      <c r="AA28" s="3" t="inlineStr">
+      <c r="AD28" s="3" t="n"/>
+      <c r="AE28" s="3" t="n"/>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRM</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>REQUEST_RESOLUTION</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="n"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>VRQ-0001</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr">
+        <is>
+          <t>(결정적 해시)</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="n"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:40+09:00</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
@@ -12713,7 +13205,7 @@
           <t>영문 테이블명</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>event_entity_link</t>
         </is>
@@ -12723,7 +13215,7 @@
           <t>한글 테이블명</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>사건 대상 연결</t>
         </is>
@@ -12733,7 +13225,7 @@
           <t>분류</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>SOURCE_OF_TRUTH</t>
         </is>
@@ -12743,7 +13235,7 @@
           <t>단계</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -12753,7 +13245,7 @@
           <t>변경 방식</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>APPEND_ONLY</t>
         </is>
@@ -12789,7 +13281,7 @@
           <t>한글 필드명</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>사건</t>
         </is>
@@ -12831,7 +13323,7 @@
           <t>entity_id</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>link_role</t>
         </is>
@@ -12981,9 +13473,9 @@
           <t>영문 테이블명</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>canonical_fact</t>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>event_verification_target</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -12991,9 +13483,9 @@
           <t>한글 테이블명</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>현재 사실</t>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>확인 대상 연결</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -13001,9 +13493,9 @@
           <t>분류</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED_MATERIALIZED</t>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>SOURCE_OF_TRUTH</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -13011,9 +13503,9 @@
           <t>단계</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>MVP</t>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>MVP · rev.2.3</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -13021,9 +13513,9 @@
           <t>변경 방식</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
-        <is>
-          <t>REBUILDABLE</t>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>APPEND_ONLY</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13527,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>한 사실의 현재 결론. 전부 지워도 event 로부터 복원되어야 한다</t>
+          <t>확인 사건이 어느 사건을 확인·기각했는지. VERIFICATION 부류의 대상 목록</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13539,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>rev.2: PK 에 적용 범위 2컬럼 추가. 예시 1·2 는 같은 시설·같은 사실 키인데 범위가 달라 공존한다 (평시 15,000원 / 이번 건만 0원). 계산은 가장 좁은 범위를 고른다. 근거 강도는 여기서 계산된다</t>
+          <t>rev.2.3 신규. docs/21 9절의 확인 부류를 논리 모델에 표현한다. JSON 배열이 아니라 연결 표인 이유는 overruled 가 Reconciliation(R1 기각)의 역방향 조회 대상이기 때문이다. verification_request_handling 이 이것을 대신하지 않는다 (A-17) / rev.2.3 보강: 한 확인 사건의 모든 대상(TARGET·OVERRULED)은 같은 현재 사실 좌표 안에 있어야 한다 — 좌표를 넘나들면 SUBJECT 1건 규칙(I-8)이 결정되지 않고 OVERRULED 가 다툰 적 없는 사실을 기각한다 (Markdown 11.2a.1 · I-26)</t>
         </is>
       </c>
     </row>
@@ -13059,167 +13551,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>개체 종류</t>
+          <t>확인 사건</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>개체 id</t>
+          <t>대상 사건</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>사실 키</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>적용 범위 종류</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>적용 범위 참조</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>사실 이름</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>파라미터 날짜</t>
-        </is>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>파라미터 슬롯</t>
-        </is>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>파라미터 규격</t>
-        </is>
-      </c>
-      <c r="K44" s="16" t="inlineStr">
-        <is>
-          <t>값(문자)</t>
-        </is>
-      </c>
-      <c r="L44" s="16" t="inlineStr">
-        <is>
-          <t>값(수치)</t>
-        </is>
-      </c>
-      <c r="M44" s="16" t="inlineStr">
-        <is>
-          <t>값(시각)</t>
-        </is>
-      </c>
-      <c r="N44" s="16" t="inlineStr">
-        <is>
-          <t>값(코드)</t>
-        </is>
-      </c>
-      <c r="O44" s="16" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="P44" s="16" t="inlineStr">
-        <is>
-          <t>적용 시작</t>
-        </is>
-      </c>
-      <c r="Q44" s="16" t="inlineStr">
-        <is>
-          <t>적용 종료</t>
-        </is>
-      </c>
-      <c r="R44" s="16" t="inlineStr">
-        <is>
-          <t>채택 사건</t>
-        </is>
-      </c>
-      <c r="S44" s="16" t="inlineStr">
-        <is>
-          <t>적용 규칙</t>
-        </is>
-      </c>
-      <c r="T44" s="16" t="inlineStr">
-        <is>
-          <t>규칙 판</t>
-        </is>
-      </c>
-      <c r="U44" s="16" t="inlineStr">
-        <is>
-          <t>검증 상태</t>
-        </is>
-      </c>
-      <c r="V44" s="16" t="inlineStr">
-        <is>
-          <t>근거 강도</t>
-        </is>
-      </c>
-      <c r="W44" s="16" t="inlineStr">
-        <is>
-          <t>근거 강도 정책 판</t>
-        </is>
-      </c>
-      <c r="X44" s="16" t="inlineStr">
-        <is>
-          <t>신뢰도</t>
-        </is>
-      </c>
-      <c r="Y44" s="16" t="inlineStr">
-        <is>
-          <t>근거 시각</t>
-        </is>
-      </c>
-      <c r="Z44" s="16" t="inlineStr">
-        <is>
-          <t>근거 시각 품질</t>
-        </is>
-      </c>
-      <c r="AA44" s="16" t="inlineStr">
-        <is>
-          <t>시간 신뢰도</t>
-        </is>
-      </c>
-      <c r="AB44" s="16" t="inlineStr">
-        <is>
-          <t>신선도 상태</t>
-        </is>
-      </c>
-      <c r="AC44" s="16" t="inlineStr">
-        <is>
-          <t>충돌 있음</t>
-        </is>
-      </c>
-      <c r="AD44" s="16" t="inlineStr">
-        <is>
-          <t>기여 사건 수</t>
-        </is>
-      </c>
-      <c r="AE44" s="16" t="inlineStr">
-        <is>
-          <t>시뮬레이션</t>
-        </is>
-      </c>
-      <c r="AF44" s="16" t="inlineStr">
-        <is>
-          <t>시나리오</t>
-        </is>
-      </c>
-      <c r="AG44" s="16" t="inlineStr">
-        <is>
-          <t>계산 기준 시각</t>
-        </is>
-      </c>
-      <c r="AH44" s="16" t="inlineStr">
-        <is>
-          <t>계산 시각</t>
+          <t>대상 역할</t>
         </is>
       </c>
     </row>
@@ -13231,167 +13573,17 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>entity_type</t>
+          <t>verification_event_id</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>target_event_id</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>fact_key</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>applicability_scope_type</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>applicability_scope_ref</t>
-        </is>
-      </c>
-      <c r="G45" s="19" t="inlineStr">
-        <is>
-          <t>fact_name</t>
-        </is>
-      </c>
-      <c r="H45" s="19" t="inlineStr">
-        <is>
-          <t>param_date</t>
-        </is>
-      </c>
-      <c r="I45" s="19" t="inlineStr">
-        <is>
-          <t>param_slot_start</t>
-        </is>
-      </c>
-      <c r="J45" s="19" t="inlineStr">
-        <is>
-          <t>param_size_type</t>
-        </is>
-      </c>
-      <c r="K45" s="19" t="inlineStr">
-        <is>
-          <t>value_text</t>
-        </is>
-      </c>
-      <c r="L45" s="19" t="inlineStr">
-        <is>
-          <t>value_number</t>
-        </is>
-      </c>
-      <c r="M45" s="19" t="inlineStr">
-        <is>
-          <t>value_timestamp</t>
-        </is>
-      </c>
-      <c r="N45" s="19" t="inlineStr">
-        <is>
-          <t>value_code</t>
-        </is>
-      </c>
-      <c r="O45" s="19" t="inlineStr">
-        <is>
-          <t>value_unit</t>
-        </is>
-      </c>
-      <c r="P45" s="19" t="inlineStr">
-        <is>
-          <t>valid_from</t>
-        </is>
-      </c>
-      <c r="Q45" s="19" t="inlineStr">
-        <is>
-          <t>valid_until</t>
-        </is>
-      </c>
-      <c r="R45" s="20" t="inlineStr">
-        <is>
-          <t>winning_event_id</t>
-        </is>
-      </c>
-      <c r="S45" s="19" t="inlineStr">
-        <is>
-          <t>applied_rule</t>
-        </is>
-      </c>
-      <c r="T45" s="19" t="inlineStr">
-        <is>
-          <t>rule_version</t>
-        </is>
-      </c>
-      <c r="U45" s="19" t="inlineStr">
-        <is>
-          <t>verification_status</t>
-        </is>
-      </c>
-      <c r="V45" s="19" t="inlineStr">
-        <is>
-          <t>evidence_strength</t>
-        </is>
-      </c>
-      <c r="W45" s="19" t="inlineStr">
-        <is>
-          <t>evidence_policy_version</t>
-        </is>
-      </c>
-      <c r="X45" s="19" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="Y45" s="19" t="inlineStr">
-        <is>
-          <t>evidence_time</t>
-        </is>
-      </c>
-      <c r="Z45" s="19" t="inlineStr">
-        <is>
-          <t>evidence_time_quality</t>
-        </is>
-      </c>
-      <c r="AA45" s="19" t="inlineStr">
-        <is>
-          <t>temporal_confidence</t>
-        </is>
-      </c>
-      <c r="AB45" s="19" t="inlineStr">
-        <is>
-          <t>freshness_status</t>
-        </is>
-      </c>
-      <c r="AC45" s="19" t="inlineStr">
-        <is>
-          <t>has_conflict</t>
-        </is>
-      </c>
-      <c r="AD45" s="19" t="inlineStr">
-        <is>
-          <t>contributing_event_count</t>
-        </is>
-      </c>
-      <c r="AE45" s="17" t="inlineStr">
-        <is>
-          <t>is_simulated</t>
-        </is>
-      </c>
-      <c r="AF45" s="20" t="inlineStr">
-        <is>
-          <t>scenario_id</t>
-        </is>
-      </c>
-      <c r="AG45" s="19" t="inlineStr">
-        <is>
-          <t>computed_as_of</t>
-        </is>
-      </c>
-      <c r="AH45" s="19" t="inlineStr">
-        <is>
-          <t>computed_at</t>
+          <t>target_role</t>
         </is>
       </c>
     </row>
@@ -13403,167 +13595,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>REF(event)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>REF(event)</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
           <t>CODE</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>STRING(30)</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>STRING(120)</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>STRING(60)</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>STRING(60)</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>DECIMAL(18,4)</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="O46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>REF(event)</t>
-        </is>
-      </c>
-      <c r="S46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="T46" s="6" t="inlineStr">
-        <is>
-          <t>STRING(20)</t>
-        </is>
-      </c>
-      <c r="U46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="V46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="W46" s="6" t="inlineStr">
-        <is>
-          <t>STRING(20)</t>
-        </is>
-      </c>
-      <c r="X46" s="6" t="inlineStr">
-        <is>
-          <t>DECIMAL(5,4)</t>
-        </is>
-      </c>
-      <c r="Y46" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="Z46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="AA46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="AB46" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="AC46" s="6" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="AD46" s="6" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="AE46" s="6" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="AF46" s="6" t="inlineStr">
-        <is>
-          <t>REF(scenario)</t>
-        </is>
-      </c>
-      <c r="AG46" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="AH46" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
         </is>
       </c>
     </row>
@@ -13575,167 +13617,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL / PK 일부 / event_class = VERIFICATION 인 행만 / 이 행의 SUBJECT·적용 범위 = 대상들의 좌표</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL / PK 일부 / VERIFICATION 은 대상이 될 수 없다 / 한 확인의 모든 대상은 같은 좌표(SUBJECT + fact_key + 적용 범위) (I-26)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 기본 GLOBAL</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / GLOBAL 이면 빈 문자열</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>파라미터 뗀 이름</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 조회용 분해</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 시간 범위</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 시간 범위</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>R1~R12</t>
-        </is>
-      </c>
-      <c r="T47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="U47" s="3" t="inlineStr">
-        <is>
-          <t>VERIFIED / INFERRED / ASSUMED / UNKNOWN / CONFLICTED</t>
-        </is>
-      </c>
-      <c r="V47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 계산 결과</t>
-        </is>
-      </c>
-      <c r="W47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 바뀌면 재계산</t>
-        </is>
-      </c>
-      <c r="X47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 3단계 폴백 결과</t>
-        </is>
-      </c>
-      <c r="Z47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="AA47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="AB47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="AC47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 캐시</t>
-        </is>
-      </c>
-      <c r="AD47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="AE47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="AF47" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="AG47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="AH47" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL / PK 일부 / TARGET / OVERRULED</t>
         </is>
       </c>
     </row>
@@ -13747,127 +13639,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>FACILITY</t>
+          <t>EVT-000120</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>FAC-WH-02</t>
+          <t>EVT-000045</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>warehouse.storage_rate</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>GLOBAL</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>warehouse.storage_rate</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
-      <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="inlineStr"/>
-      <c r="Q48" s="3" t="inlineStr"/>
-      <c r="R48" s="3" t="inlineStr">
-        <is>
-          <t>EVT-000030</t>
-        </is>
-      </c>
-      <c r="S48" s="3" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="T48" s="3" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="U48" s="3" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="V48" s="3" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="W48" s="3" t="inlineStr">
-        <is>
-          <t>ev-v1</t>
-        </is>
-      </c>
-      <c r="X48" s="3" t="inlineStr">
-        <is>
-          <t>0.9000</t>
-        </is>
-      </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:00+09:00</t>
-        </is>
-      </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>SOURCE_EVENT_TIME</t>
-        </is>
-      </c>
-      <c r="AA48" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="AB48" s="3" t="inlineStr">
-        <is>
-          <t>FRESH</t>
-        </is>
-      </c>
-      <c r="AC48" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AD48" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE48" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AF48" s="3" t="inlineStr"/>
-      <c r="AG48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:05+09:00</t>
-        </is>
-      </c>
-      <c r="AH48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:05+09:00</t>
+          <t>TARGET</t>
         </is>
       </c>
     </row>
@@ -13879,1347 +13661,1749 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>FACILITY</t>
+          <t>EVT-000120</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>FAC-WH-02</t>
+          <t>EVT-000030</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>warehouse.storage_rate</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>RECOVERY_CONTEXT</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>warehouse.storage_rate</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
-      <c r="K49" s="3" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr"/>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T00:00+09:00</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr"/>
-      <c r="R49" s="3" t="inlineStr">
-        <is>
-          <t>EVT-000077</t>
-        </is>
-      </c>
-      <c r="S49" s="3" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="T49" s="3" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="U49" s="3" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="V49" s="3" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="W49" s="3" t="inlineStr">
-        <is>
-          <t>ev-v1</t>
-        </is>
-      </c>
-      <c r="X49" s="3" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:00+09:00</t>
-        </is>
-      </c>
-      <c r="Z49" s="3" t="inlineStr">
-        <is>
-          <t>SOURCE_EVENT_TIME</t>
-        </is>
-      </c>
-      <c r="AA49" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="AB49" s="3" t="inlineStr">
-        <is>
-          <t>FRESH</t>
-        </is>
-      </c>
-      <c r="AC49" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AD49" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE49" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AF49" s="3" t="inlineStr"/>
-      <c r="AG49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:05+09:00</t>
-        </is>
-      </c>
-      <c r="AH49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:05+09:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>예시 3</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>FACILITY</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>FAC-WH-01</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>warehouse.capacity@2026-09-18</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>GLOBAL</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>warehouse.capacity</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="3" t="inlineStr"/>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr"/>
-      <c r="N50" s="3" t="inlineStr"/>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>TEU</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T00:00+09:00</t>
-        </is>
-      </c>
-      <c r="Q50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T23:59+09:00</t>
-        </is>
-      </c>
-      <c r="R50" s="3" t="inlineStr">
-        <is>
-          <t>EVT-000045</t>
-        </is>
-      </c>
-      <c r="S50" s="3" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="T50" s="3" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="U50" s="3" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="V50" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="W50" s="3" t="inlineStr">
-        <is>
-          <t>ev-v1</t>
-        </is>
-      </c>
-      <c r="X50" s="3" t="inlineStr">
-        <is>
-          <t>0.7000</t>
-        </is>
-      </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T08:20+09:00</t>
-        </is>
-      </c>
-      <c r="Z50" s="3" t="inlineStr">
-        <is>
-          <t>SOURCE_EVENT_TIME</t>
-        </is>
-      </c>
-      <c r="AA50" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="AB50" s="3" t="inlineStr">
-        <is>
-          <t>FRESH</t>
-        </is>
-      </c>
-      <c r="AC50" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AD50" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE50" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AF50" s="3" t="inlineStr"/>
-      <c r="AG50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T09:00+09:00</t>
-        </is>
-      </c>
-      <c r="AH50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T09:00+09:00</t>
+          <t>OVERRULED</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>영문 테이블명</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>canonical_fact</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>한글 테이블명</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>현재 사실</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>DERIVED_MATERIALIZED</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>변경 방식</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>REBUILDABLE</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>영문 테이블명</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>conflict</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>한글 테이블명</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>충돌</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>분류</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED_MATERIALIZED</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>변경 방식</t>
-        </is>
-      </c>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>REBUILDABLE</t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>한 사실의 현재 결론. 전부 지워도 event 로부터 복원되어야 한다</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>주의</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>자동으로 정할 근거가 없는 차이. 같은 적용 범위 안에서만 생긴다</t>
+          <t>rev.2: PK 에 적용 범위 2컬럼 추가. 예시 1·2 는 같은 시설·같은 사실 키인데 범위가 달라 공존한다 (평시 15,000원 / 이번 건만 0원). 계산은 가장 좁은 범위를 고른다. 근거 강도는 여기서 계산된다 / rev.2.3: ADR-020 의 상태 차원을 복구했다 — value_status · freshness_status · conflict_status · hold_status · decision_usability + verification_basis. 의미가 정의된 적 없는 confidence 는 제거했다 (Markdown 11.4.2) / rev.2.3 보강: decision_usability 는 저장하지만 원천이 아니다. (네 차원, rule_version, 중요도 정책 판) 이 같으면 항상 같은 값 (I-24)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>주의</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>rev.2.1: 적용 범위 2컬럼 추가. GLOBAL 15,000원과 RECOVERY_CONTEXT 0원은 서로 다투는 주장이 아니므로 같은 충돌에 들어가면 안 된다. 충돌의 해소는 여기 쓰지 않는다</t>
+          <t>한글 필드명</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>개체 종류</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>개체 id</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>사실 키</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>적용 범위 종류</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>적용 범위 참조</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>사실 이름</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>파라미터 날짜</t>
+        </is>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>파라미터 슬롯</t>
+        </is>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>파라미터 규격</t>
+        </is>
+      </c>
+      <c r="K54" s="16" t="inlineStr">
+        <is>
+          <t>값(문자)</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>값(수치)</t>
+        </is>
+      </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>값(시각)</t>
+        </is>
+      </c>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>값(코드)</t>
+        </is>
+      </c>
+      <c r="O54" s="16" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="P54" s="16" t="inlineStr">
+        <is>
+          <t>적용 시작</t>
+        </is>
+      </c>
+      <c r="Q54" s="16" t="inlineStr">
+        <is>
+          <t>적용 종료</t>
+        </is>
+      </c>
+      <c r="R54" s="16" t="inlineStr">
+        <is>
+          <t>채택 사건</t>
+        </is>
+      </c>
+      <c r="S54" s="16" t="inlineStr">
+        <is>
+          <t>적용 규칙</t>
+        </is>
+      </c>
+      <c r="T54" s="16" t="inlineStr">
+        <is>
+          <t>규칙 판</t>
+        </is>
+      </c>
+      <c r="U54" s="16" t="inlineStr">
+        <is>
+          <t>값 보증</t>
+        </is>
+      </c>
+      <c r="V54" s="16" t="inlineStr">
+        <is>
+          <t>확인 근거</t>
+        </is>
+      </c>
+      <c r="W54" s="16" t="inlineStr">
+        <is>
+          <t>근거 강도</t>
+        </is>
+      </c>
+      <c r="X54" s="16" t="inlineStr">
+        <is>
+          <t>근거 강도 정책 판</t>
+        </is>
+      </c>
+      <c r="Y54" s="16" t="inlineStr">
+        <is>
+          <t>근거 시각</t>
+        </is>
+      </c>
+      <c r="Z54" s="16" t="inlineStr">
+        <is>
+          <t>근거 시각 품질</t>
+        </is>
+      </c>
+      <c r="AA54" s="16" t="inlineStr">
+        <is>
+          <t>시간 신뢰도</t>
+        </is>
+      </c>
+      <c r="AB54" s="16" t="inlineStr">
+        <is>
+          <t>신선도 상태</t>
+        </is>
+      </c>
+      <c r="AC54" s="16" t="inlineStr">
+        <is>
+          <t>충돌 상태</t>
+        </is>
+      </c>
+      <c r="AD54" s="16" t="inlineStr">
+        <is>
+          <t>보류 상태</t>
+        </is>
+      </c>
+      <c r="AE54" s="16" t="inlineStr">
+        <is>
+          <t>결정 가능성</t>
+        </is>
+      </c>
+      <c r="AF54" s="16" t="inlineStr">
+        <is>
+          <t>기여 사건 수</t>
+        </is>
+      </c>
+      <c r="AG54" s="16" t="inlineStr">
+        <is>
+          <t>시뮬레이션</t>
+        </is>
+      </c>
+      <c r="AH54" s="16" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="AI54" s="16" t="inlineStr">
+        <is>
+          <t>계산 기준 시각</t>
+        </is>
+      </c>
+      <c r="AJ54" s="16" t="inlineStr">
+        <is>
+          <t>계산 시각</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>한글 필드명</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>충돌 id</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>개체 종류</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>개체 id</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>사실 키</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>적용 범위 종류</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>적용 범위 참조</t>
-        </is>
-      </c>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>충돌 종류</t>
-        </is>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>대립 사건들</t>
-        </is>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>심각도</t>
-        </is>
-      </c>
-      <c r="K55" s="16" t="inlineStr">
-        <is>
-          <t>탐지 규칙</t>
-        </is>
-      </c>
-      <c r="L55" s="16" t="inlineStr">
-        <is>
-          <t>규칙 판</t>
-        </is>
-      </c>
-      <c r="M55" s="16" t="inlineStr">
-        <is>
-          <t>자동화 차단</t>
-        </is>
-      </c>
-      <c r="N55" s="16" t="inlineStr">
-        <is>
-          <t>계산 기준 시각</t>
-        </is>
-      </c>
-      <c r="O55" s="16" t="inlineStr">
-        <is>
-          <t>시뮬레이션</t>
-        </is>
-      </c>
-      <c r="P55" s="16" t="inlineStr">
-        <is>
-          <t>시나리오</t>
+          <t>영문 필드명</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>entity_type</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>fact_key</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>applicability_scope_type</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>applicability_scope_ref</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>fact_name</t>
+        </is>
+      </c>
+      <c r="H55" s="17" t="inlineStr">
+        <is>
+          <t>param_date</t>
+        </is>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>param_slot_start</t>
+        </is>
+      </c>
+      <c r="J55" s="17" t="inlineStr">
+        <is>
+          <t>param_size_type</t>
+        </is>
+      </c>
+      <c r="K55" s="17" t="inlineStr">
+        <is>
+          <t>value_text</t>
+        </is>
+      </c>
+      <c r="L55" s="17" t="inlineStr">
+        <is>
+          <t>value_number</t>
+        </is>
+      </c>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>value_timestamp</t>
+        </is>
+      </c>
+      <c r="N55" s="17" t="inlineStr">
+        <is>
+          <t>value_code</t>
+        </is>
+      </c>
+      <c r="O55" s="17" t="inlineStr">
+        <is>
+          <t>value_unit</t>
+        </is>
+      </c>
+      <c r="P55" s="17" t="inlineStr">
+        <is>
+          <t>valid_from</t>
+        </is>
+      </c>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>valid_until</t>
+        </is>
+      </c>
+      <c r="R55" s="17" t="inlineStr">
+        <is>
+          <t>winning_event_id</t>
+        </is>
+      </c>
+      <c r="S55" s="17" t="inlineStr">
+        <is>
+          <t>applied_rule</t>
+        </is>
+      </c>
+      <c r="T55" s="17" t="inlineStr">
+        <is>
+          <t>rule_version</t>
+        </is>
+      </c>
+      <c r="U55" s="17" t="inlineStr">
+        <is>
+          <t>value_status</t>
+        </is>
+      </c>
+      <c r="V55" s="17" t="inlineStr">
+        <is>
+          <t>verification_basis</t>
+        </is>
+      </c>
+      <c r="W55" s="17" t="inlineStr">
+        <is>
+          <t>evidence_strength</t>
+        </is>
+      </c>
+      <c r="X55" s="17" t="inlineStr">
+        <is>
+          <t>evidence_policy_version</t>
+        </is>
+      </c>
+      <c r="Y55" s="17" t="inlineStr">
+        <is>
+          <t>evidence_time</t>
+        </is>
+      </c>
+      <c r="Z55" s="17" t="inlineStr">
+        <is>
+          <t>evidence_time_quality</t>
+        </is>
+      </c>
+      <c r="AA55" s="17" t="inlineStr">
+        <is>
+          <t>temporal_confidence</t>
+        </is>
+      </c>
+      <c r="AB55" s="17" t="inlineStr">
+        <is>
+          <t>freshness_status</t>
+        </is>
+      </c>
+      <c r="AC55" s="17" t="inlineStr">
+        <is>
+          <t>conflict_status</t>
+        </is>
+      </c>
+      <c r="AD55" s="17" t="inlineStr">
+        <is>
+          <t>hold_status</t>
+        </is>
+      </c>
+      <c r="AE55" s="17" t="inlineStr">
+        <is>
+          <t>decision_usability</t>
+        </is>
+      </c>
+      <c r="AF55" s="17" t="inlineStr">
+        <is>
+          <t>contributing_event_count</t>
+        </is>
+      </c>
+      <c r="AG55" s="17" t="inlineStr">
+        <is>
+          <t>is_simulated</t>
+        </is>
+      </c>
+      <c r="AH55" s="17" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="AI55" s="17" t="inlineStr">
+        <is>
+          <t>computed_as_of</t>
+        </is>
+      </c>
+      <c r="AJ55" s="17" t="inlineStr">
+        <is>
+          <t>computed_at</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>영문 필드명</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>conflict_id</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>entity_type</t>
-        </is>
-      </c>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>entity_id</t>
-        </is>
-      </c>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>fact_key</t>
-        </is>
-      </c>
-      <c r="F56" s="19" t="inlineStr">
-        <is>
-          <t>applicability_scope_type</t>
-        </is>
-      </c>
-      <c r="G56" s="19" t="inlineStr">
-        <is>
-          <t>applicability_scope_ref</t>
-        </is>
-      </c>
-      <c r="H56" s="19" t="inlineStr">
-        <is>
-          <t>conflict_type</t>
-        </is>
-      </c>
-      <c r="I56" s="19" t="inlineStr">
-        <is>
-          <t>event_ids</t>
-        </is>
-      </c>
-      <c r="J56" s="19" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="K56" s="19" t="inlineStr">
-        <is>
-          <t>detected_rule</t>
-        </is>
-      </c>
-      <c r="L56" s="19" t="inlineStr">
-        <is>
-          <t>rule_version</t>
-        </is>
-      </c>
-      <c r="M56" s="19" t="inlineStr">
-        <is>
-          <t>blocks_automation</t>
-        </is>
-      </c>
-      <c r="N56" s="19" t="inlineStr">
-        <is>
-          <t>computed_as_of</t>
-        </is>
-      </c>
-      <c r="O56" s="19" t="inlineStr">
-        <is>
-          <t>is_simulated</t>
-        </is>
-      </c>
-      <c r="P56" s="20" t="inlineStr">
-        <is>
-          <t>scenario_id</t>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>STRING(30)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>STRING(120)</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>STRING(60)</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>STRING(60)</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>DECIMAL(18,4)</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>REF(event)</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="T56" s="6" t="inlineStr">
+        <is>
+          <t>STRING(20)</t>
+        </is>
+      </c>
+      <c r="U56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="V56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="W56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="X56" s="6" t="inlineStr">
+        <is>
+          <t>STRING(20)</t>
+        </is>
+      </c>
+      <c r="Y56" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="Z56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AA56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AB56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AC56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AD56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AE56" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AF56" s="6" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="AG56" s="6" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="AH56" s="6" t="inlineStr">
+        <is>
+          <t>REF(scenario)</t>
+        </is>
+      </c>
+      <c r="AI56" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="AJ56" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>타입</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>STRING(40)</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>STRING(30)</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>STRING(120)</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>STRING(60)</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="L57" s="6" t="inlineStr">
-        <is>
-          <t>STRING(20)</t>
-        </is>
-      </c>
-      <c r="M57" s="6" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="N57" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="O57" s="6" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>REF(scenario)</t>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 기본 GLOBAL</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / GLOBAL 이면 빈 문자열</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>파라미터 뗀 이름</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 조회용 분해</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 시간 범위</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 시간 범위</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>R1~R12</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / CONFIRMED / OBSERVED / PROVISIONAL / INFERRED / UNKNOWN / rev.2.3 교체</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRMED 이면 NOT NULL / HUMAN_VERIFICATION / AUTHORITATIVE_SYSTEM / POLICY_EVIDENCE / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 계산 결과</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 바뀌면 재계산</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 3단계 폴백 결과</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / NONE / DISSENT / OPEN / rev.2.3 교체 (옛 BOOLEAN)</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / NONE / HELD (R10) / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / USABLE / USABLE_WITH_WARNING / APPROVAL_BLOCKED / UNUSABLE / 파생 - 네 차원 + 중요도 정책에서 R11 로 유도 (I-24). 독립 입력 아님</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>제약</t>
+      <c r="A58" s="21" t="inlineStr">
+        <is>
+          <t>예시 1</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>FACILITY</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>FAC-WH-02</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>warehouse.storage_rate</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / rev.2.1 신규</t>
-        </is>
-      </c>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL / rev.2.1 신규</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 같은 범위의 사건만</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
+          <t>warehouse.storage_rate</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="n"/>
+      <c r="N58" s="3" t="n"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="n"/>
+      <c r="Q58" s="3" t="n"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>EVT-000030</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>HUMAN_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>ev-v1</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:00+09:00</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>SOURCE_EVENT_TIME</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>FRESH</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>USABLE</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="n"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05+09:00</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>예시 1</t>
+          <t>예시 2</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CFL-0001</t>
+          <t>FACILITY</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
+          <t>FAC-WH-02</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>warehouse.storage_rate</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>RECOVERY_CONTEXT</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>warehouse.storage_rate</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="n"/>
+      <c r="N59" s="3" t="n"/>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T00:00+09:00</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="n"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>EVT-000077</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>HUMAN_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>ev-v1</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:00+09:00</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>SOURCE_EVENT_TIME</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>FRESH</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>USABLE</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="n"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05+09:00</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t>예시 3</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
           <t>FACILITY</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>FAC-WH-01</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>warehouse.capacity@2026-09-18</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>VALUE_MISMATCH</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>["EVT-000045","EVT-000051"]</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>warehouse.capacity</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3" t="n"/>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>TEU</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T00:00+09:00</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:59+09:00</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>EVT-000045</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="T60" s="3" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="N59" s="3" t="inlineStr">
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="n"/>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>ev-v1</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T08:20+09:00</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>SOURCE_EVENT_TIME</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>FRESH</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>APPROVAL_BLOCKED</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="n"/>
+      <c r="AI60" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T09:00+09:00</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="n">
+      <c r="AJ60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>영문 테이블명</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>verification_request</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>한글 테이블명</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>확인 요청</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>충돌</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>DERIVED_MATERIALIZED</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="J61" s="8" t="inlineStr">
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>변경 방식</t>
         </is>
       </c>
-      <c r="K61" s="9" t="inlineStr">
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>REBUILDABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>사람에게 물어야 할 항목. 재계산으로 다시 만들어진다</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>주의</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>rev.2.1: 적용 범위 2컬럼 추가. request_key 재료 = trigger_rule + 개체 + fact_key + 적용 범위 + 불변 사건 id 집합. 파생 대리키(conflict_id)는 재료로 쓰지 않는다 (Q-59)</t>
+          <t>자동으로 정할 근거가 없는 차이. 같은 적용 범위 안에서만 생긴다</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>한글 필드명</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>요청 id</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>요청 키</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>발생 규칙</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>개체 종류</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>개체 id</t>
-        </is>
-      </c>
-      <c r="G64" s="16" t="inlineStr">
-        <is>
-          <t>사실 키</t>
-        </is>
-      </c>
-      <c r="H64" s="16" t="inlineStr">
-        <is>
-          <t>적용 범위 종류</t>
-        </is>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>적용 범위 참조</t>
-        </is>
-      </c>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>관련 충돌</t>
-        </is>
-      </c>
-      <c r="K64" s="16" t="inlineStr">
-        <is>
-          <t>우선순위</t>
-        </is>
-      </c>
-      <c r="L64" s="16" t="inlineStr">
-        <is>
-          <t>자동화 차단</t>
-        </is>
-      </c>
-      <c r="M64" s="16" t="inlineStr">
-        <is>
-          <t>계산 기준 시각</t>
-        </is>
-      </c>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>계산 시각</t>
-        </is>
-      </c>
-      <c r="O64" s="16" t="inlineStr">
-        <is>
-          <t>현재 처리 상태</t>
-        </is>
-      </c>
-      <c r="P64" s="16" t="inlineStr">
-        <is>
-          <t>시뮬레이션</t>
-        </is>
-      </c>
-      <c r="Q64" s="16" t="inlineStr">
-        <is>
-          <t>시나리오</t>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>rev.2.1: 적용 범위 2컬럼 추가. GLOBAL 15,000원과 RECOVERY_CONTEXT 0원은 서로 다투는 주장이 아니므로 같은 충돌에 들어가면 안 된다. 충돌의 해소는 여기 쓰지 않는다</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>영문 필드명</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>verification_request_id</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="inlineStr">
-        <is>
-          <t>request_key</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>trigger_rule</t>
-        </is>
-      </c>
-      <c r="E65" s="19" t="inlineStr">
-        <is>
-          <t>entity_type</t>
-        </is>
-      </c>
-      <c r="F65" s="19" t="inlineStr">
-        <is>
-          <t>entity_id</t>
-        </is>
-      </c>
-      <c r="G65" s="19" t="inlineStr">
-        <is>
-          <t>fact_key</t>
-        </is>
-      </c>
-      <c r="H65" s="19" t="inlineStr">
-        <is>
-          <t>applicability_scope_type</t>
-        </is>
-      </c>
-      <c r="I65" s="19" t="inlineStr">
-        <is>
-          <t>applicability_scope_ref</t>
-        </is>
-      </c>
-      <c r="J65" s="20" t="inlineStr">
-        <is>
-          <t>conflict_id</t>
-        </is>
-      </c>
-      <c r="K65" s="19" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="L65" s="19" t="inlineStr">
-        <is>
-          <t>blocks_automation</t>
-        </is>
-      </c>
-      <c r="M65" s="19" t="inlineStr">
-        <is>
-          <t>computed_as_of</t>
-        </is>
-      </c>
-      <c r="N65" s="19" t="inlineStr">
-        <is>
-          <t>computed_at</t>
-        </is>
-      </c>
-      <c r="O65" s="19" t="inlineStr">
-        <is>
-          <t>current_status</t>
-        </is>
-      </c>
-      <c r="P65" s="19" t="inlineStr">
-        <is>
-          <t>is_simulated</t>
-        </is>
-      </c>
-      <c r="Q65" s="20" t="inlineStr">
-        <is>
-          <t>scenario_id</t>
+          <t>한글 필드명</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>충돌 id</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>개체 종류</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>개체 id</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>사실 키</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>적용 범위 종류</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>적용 범위 참조</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>충돌 종류</t>
+        </is>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>대립 사건들</t>
+        </is>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>심각도</t>
+        </is>
+      </c>
+      <c r="K65" s="16" t="inlineStr">
+        <is>
+          <t>탐지 규칙</t>
+        </is>
+      </c>
+      <c r="L65" s="16" t="inlineStr">
+        <is>
+          <t>규칙 판</t>
+        </is>
+      </c>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>자동화 차단</t>
+        </is>
+      </c>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>계산 기준 시각</t>
+        </is>
+      </c>
+      <c r="O65" s="16" t="inlineStr">
+        <is>
+          <t>시뮬레이션</t>
+        </is>
+      </c>
+      <c r="P65" s="16" t="inlineStr">
+        <is>
+          <t>시나리오</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>타입</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>STRING(40)</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>HASH</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>STRING(30)</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>STRING(120)</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>STRING(60)</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>REF(conflict)</t>
-        </is>
-      </c>
-      <c r="K66" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="L66" s="6" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="M66" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="N66" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_TZ</t>
-        </is>
-      </c>
-      <c r="O66" s="6" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="P66" s="6" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="Q66" s="6" t="inlineStr">
-        <is>
-          <t>REF(scenario)</t>
+          <t>영문 필드명</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>conflict_id</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>entity_type</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>fact_key</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>applicability_scope_type</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>applicability_scope_ref</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>conflict_type</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>event_ids</t>
+        </is>
+      </c>
+      <c r="J66" s="17" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
+          <t>detected_rule</t>
+        </is>
+      </c>
+      <c r="L66" s="17" t="inlineStr">
+        <is>
+          <t>rule_version</t>
+        </is>
+      </c>
+      <c r="M66" s="17" t="inlineStr">
+        <is>
+          <t>blocks_automation</t>
+        </is>
+      </c>
+      <c r="N66" s="17" t="inlineStr">
+        <is>
+          <t>computed_as_of</t>
+        </is>
+      </c>
+      <c r="O66" s="17" t="inlineStr">
+        <is>
+          <t>is_simulated</t>
+        </is>
+      </c>
+      <c r="P66" s="17" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>STRING(40)</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>STRING(30)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>STRING(120)</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>STRING(60)</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>STRING(20)</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>REF(scenario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 파생 대리키</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 결정적 - 파생 대리키 사용 금지</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL / rev.2.1 신규</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL / rev.2.1 신규</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 화면용 참조 - request_key 재료 아님</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="L67" s="3" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 같은 범위의 사건만</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="M67" s="3" t="inlineStr">
+      <c r="K68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="N67" s="3" t="inlineStr">
+      <c r="L68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 캐시</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="inlineStr">
+      <c r="M68" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="Q67" s="3" t="inlineStr">
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="21" t="inlineStr">
-        <is>
-          <t>예시 1</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>VRQ-0001</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>(결정적 해시)</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>CONFLICT_UNRESOLVED</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>FACILITY</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>FAC-WH-01</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>warehouse.capacity@2026-09-18</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>GLOBAL</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>CFL-0001</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T09:00+09:00</t>
-        </is>
-      </c>
-      <c r="N68" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T09:00+09:00</t>
-        </is>
-      </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>ASKED_EXTERNAL</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="Q68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>예시 2</t>
+          <t>예시 1</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>VRQ-0007</t>
+          <t>CFL-0001</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>(결정적 해시)</t>
+          <t>FACILITY</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>OPERATOR_INPUT_CHECK</t>
+          <t>FAC-WH-01</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>FACILITY</t>
+          <t>warehouse.capacity@2026-09-18</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>FAC-WH-02</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>warehouse.storage_rate</t>
-        </is>
-      </c>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n"/>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>RECOVERY_CONTEXT</t>
+          <t>VALUE_MISMATCH</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr"/>
+          <t>["EVT-000045","EVT-000051"]</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:00+09:00</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:05+09:00</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:05+09:00</t>
-        </is>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>ACKNOWLEDGED</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
@@ -15230,9 +15414,9 @@
           <t>영문 테이블명</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>verification_request_handling</t>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>verification_request</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -15240,9 +15424,9 @@
           <t>한글 테이블명</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>확인 요청 처리 기록</t>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>확인 요청</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -15250,9 +15434,9 @@
           <t>분류</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>DECISION_RECORD</t>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>DERIVED_MATERIALIZED</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -15260,7 +15444,7 @@
           <t>단계</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -15270,9 +15454,9 @@
           <t>변경 방식</t>
         </is>
       </c>
-      <c r="K71" s="9" t="inlineStr">
-        <is>
-          <t>APPEND_ONLY</t>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>REBUILDABLE</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15468,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>사람의 열람/미룸/처리 이력. 재계산으로 지워지지 않는다</t>
+          <t>사람에게 물어야 할 항목. 재계산으로 다시 만들어진다</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15480,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>rev.2: request_key 는 DB 외래키가 아니라 오래 사는 논리 연결 키다. 요청이 재생성으로 사라져도 처리 기록은 남는다(고아 허용). 외래키 색으로 칠하지 않는다</t>
+          <t>rev.2.1: 적용 범위 2컬럼 추가. request_key 재료 = trigger_rule + 개체 + fact_key + 적용 범위 + 불변 사건 id 집합. 파생 대리키(conflict_id)는 재료로 쓰지 않는다 (Q-59)</t>
         </is>
       </c>
     </row>
@@ -15308,7 +15492,7 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>처리 id</t>
+          <t>요청 id</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
@@ -15318,37 +15502,72 @@
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>처리 종류</t>
+          <t>발생 규칙</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>처리 주체</t>
+          <t>개체 종류</t>
         </is>
       </c>
       <c r="F74" s="16" t="inlineStr">
         <is>
-          <t>처리 시각</t>
+          <t>개체 id</t>
         </is>
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>메모</t>
+          <t>사실 키</t>
         </is>
       </c>
       <c r="H74" s="16" t="inlineStr">
         <is>
-          <t>연결된 질문</t>
+          <t>적용 범위 종류</t>
         </is>
       </c>
       <c r="I74" s="16" t="inlineStr">
         <is>
-          <t>해소 사건</t>
+          <t>적용 범위 참조</t>
         </is>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
+          <t>관련 충돌</t>
+        </is>
+      </c>
+      <c r="K74" s="16" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="L74" s="16" t="inlineStr">
+        <is>
+          <t>자동화 차단</t>
+        </is>
+      </c>
+      <c r="M74" s="16" t="inlineStr">
+        <is>
+          <t>계산 기준 시각</t>
+        </is>
+      </c>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>계산 시각</t>
+        </is>
+      </c>
+      <c r="O74" s="16" t="inlineStr">
+        <is>
+          <t>현재 처리 상태</t>
+        </is>
+      </c>
+      <c r="P74" s="16" t="inlineStr">
+        <is>
           <t>시뮬레이션</t>
+        </is>
+      </c>
+      <c r="Q74" s="16" t="inlineStr">
+        <is>
+          <t>시나리오</t>
         </is>
       </c>
     </row>
@@ -15360,47 +15579,82 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>handling_id</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
+          <t>verification_request_id</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
         <is>
           <t>request_key</t>
         </is>
       </c>
-      <c r="D75" s="19" t="inlineStr">
-        <is>
-          <t>handling_type</t>
-        </is>
-      </c>
-      <c r="E75" s="20" t="inlineStr">
-        <is>
-          <t>actor_id</t>
-        </is>
-      </c>
-      <c r="F75" s="19" t="inlineStr">
-        <is>
-          <t>handled_at</t>
-        </is>
-      </c>
-      <c r="G75" s="19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="H75" s="20" t="inlineStr">
-        <is>
-          <t>question_item_id</t>
-        </is>
-      </c>
-      <c r="I75" s="20" t="inlineStr">
-        <is>
-          <t>resolving_event_id</t>
-        </is>
-      </c>
-      <c r="J75" s="19" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>trigger_rule</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>entity_type</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>fact_key</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
+        <is>
+          <t>applicability_scope_type</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>applicability_scope_ref</t>
+        </is>
+      </c>
+      <c r="J75" s="17" t="inlineStr">
+        <is>
+          <t>conflict_id</t>
+        </is>
+      </c>
+      <c r="K75" s="17" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="L75" s="17" t="inlineStr">
+        <is>
+          <t>blocks_automation</t>
+        </is>
+      </c>
+      <c r="M75" s="17" t="inlineStr">
+        <is>
+          <t>computed_as_of</t>
+        </is>
+      </c>
+      <c r="N75" s="17" t="inlineStr">
+        <is>
+          <t>computed_at</t>
+        </is>
+      </c>
+      <c r="O75" s="17" t="inlineStr">
+        <is>
+          <t>current_status</t>
+        </is>
+      </c>
+      <c r="P75" s="17" t="inlineStr">
         <is>
           <t>is_simulated</t>
+        </is>
+      </c>
+      <c r="Q75" s="17" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
         </is>
       </c>
     </row>
@@ -15427,32 +15681,67 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>REF(actor)</t>
+          <t>CODE</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
+          <t>STRING(30)</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>STRING(120)</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>STRING(60)</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>REF(conflict)</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>STRING(500)</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>REF(question_item)</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>REF(event)</t>
-        </is>
-      </c>
-      <c r="J76" s="6" t="inlineStr">
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>REF(scenario)</t>
         </is>
       </c>
     </row>
@@ -15464,19 +15753,19 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
+          <t>NOT NULL / 파생 대리키</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 결정적 - 파생 대리키 사용 금지</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 논리 연결 키 - DB FK 아님</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>ACKNOWLEDGED / ASSIGNED / ASKED_EXTERNAL / RESOLVED / DISMISSED / SNOOZED</t>
-        </is>
-      </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
@@ -15489,22 +15778,57 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / rev.2.1 신규</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / rev.2.1 신규</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 화면용 참조 - request_key 재료 아님</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 캐시</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
           <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15840,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>VRH-0001</t>
+          <t>VRQ-0001</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -15526,27 +15850,66 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>ACKNOWLEDGED</t>
+          <t>CONFLICT_UNRESOLVED</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>ACT-USR-01</t>
+          <t>FACILITY</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18T09:05+09:00</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr"/>
+          <t>FAC-WH-01</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>warehouse.capacity@2026-09-18</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="n"/>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>CFL-0001</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:00+09:00</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:00+09:00</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>ASKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
           <t>FALSE</t>
         </is>
       </c>
+      <c r="Q78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="21" t="inlineStr">
@@ -15556,41 +15919,447 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
+          <t>VRQ-0007</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>(결정적 해시)</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>OPERATOR_INPUT_CHECK</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>FACILITY</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>FAC-WH-02</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>warehouse.storage_rate</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>RECOVERY_CONTEXT</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>&lt;RECOVERY_CONTEXT_REF&gt;</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05+09:00</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05+09:00</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>ACKNOWLEDGED</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>영문 테이블명</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>verification_request_handling</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>한글 테이블명</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>확인 요청 처리 기록</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>DECISION_RECORD</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>변경 방식</t>
+        </is>
+      </c>
+      <c r="K81" s="8" t="inlineStr">
+        <is>
+          <t>APPEND_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>사람의 열람/미룸/처리 이력. 재계산으로 지워지지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>rev.2: request_key 는 DB 외래키가 아니라 오래 사는 논리 연결 키다. 요청이 재생성으로 사라져도 처리 기록은 남는다(고아 허용). 외래키 색으로 칠하지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>한글 필드명</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>처리 id</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>요청 키</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>처리 종류</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>처리 주체</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>처리 시각</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+      <c r="H84" s="16" t="inlineStr">
+        <is>
+          <t>연결된 질문</t>
+        </is>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>해소 사건</t>
+        </is>
+      </c>
+      <c r="J84" s="16" t="inlineStr">
+        <is>
+          <t>시뮬레이션</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>영문 필드명</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>handling_id</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>request_key</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr">
+        <is>
+          <t>handling_type</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>actor_id</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>handled_at</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="inlineStr">
+        <is>
+          <t>question_item_id</t>
+        </is>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>resolving_event_id</t>
+        </is>
+      </c>
+      <c r="J85" s="17" t="inlineStr">
+        <is>
+          <t>is_simulated</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>STRING(40)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>HASH</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>REF(actor)</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>STRING(500)</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>REF(question_item)</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>REF(event)</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 논리 연결 키 - DB FK 아님</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>ACKNOWLEDGED / ASSIGNED / ASKED_EXTERNAL / RESOLVED / DISMISSED / SNOOZED</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="inlineStr">
+        <is>
+          <t>예시 1</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>VRH-0001</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>(결정적 해시)</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>ACKNOWLEDGED</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ACT-USR-01</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:05+09:00</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>예시 2</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
           <t>VRH-0002</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>(결정적 해시)</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>ASKED_EXTERNAL</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>ACT-USR-01</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T09:12+09:00</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>창고에 확인 요청 (예시)</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>QI-0001</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -17491,7 +18260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18109,7 +18878,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>rev.2: PK 에 적용 범위 2컬럼 추가. 어느 범위의 사실을 썼는지까지 얼린다. canonical_fact 는 재계산으로 덮어써지므로 값을 복사한다 (안티패턴 7)</t>
+          <t>rev.2: PK 에 적용 범위 2컬럼 추가. 어느 범위의 사실을 썼는지까지 얼린다. canonical_fact 는 재계산으로 덮어써지므로 값을 복사한다 (안티패턴 7) / rev.2.3: 당시 상태 6차원과 판(version)을 함께 얼린다. I-12 가 "그때 왜 승인 가능했나"까지 넓어졌다 (Markdown 13.2.1) / rev.2.3: verification_status -&gt; value_status 로, 의미 없던 confidence 는 제거 (canonical_fact 와 같은 이름을 쓴다) / rev.2.3 보강: R11 판정의 입력(네 차원)과 판(rule_version + 부모 policy_version)이 모두 얼려져 있어 과거 decision_usability 판정을 그대로 재현할 수 있다 (I-27)</t>
         </is>
       </c>
     </row>
@@ -18191,19 +18960,66 @@
       </c>
       <c r="P20" s="16" t="inlineStr">
         <is>
-          <t>검증 상태</t>
-        </is>
-      </c>
-      <c r="Q20" s="16" t="inlineStr">
-        <is>
           <t>근거 강도</t>
         </is>
       </c>
-      <c r="R20" s="16" t="inlineStr">
-        <is>
-          <t>신뢰도</t>
-        </is>
-      </c>
+      <c r="Q20" s="22" t="inlineStr">
+        <is>
+          <t>값 보증</t>
+        </is>
+      </c>
+      <c r="R20" s="22" t="inlineStr">
+        <is>
+          <t>확인 근거</t>
+        </is>
+      </c>
+      <c r="S20" s="22" t="inlineStr">
+        <is>
+          <t>신선도 상태</t>
+        </is>
+      </c>
+      <c r="T20" s="22" t="inlineStr">
+        <is>
+          <t>충돌 상태</t>
+        </is>
+      </c>
+      <c r="U20" s="22" t="inlineStr">
+        <is>
+          <t>보류 상태</t>
+        </is>
+      </c>
+      <c r="V20" s="22" t="inlineStr">
+        <is>
+          <t>결정 가능성</t>
+        </is>
+      </c>
+      <c r="W20" s="22" t="inlineStr">
+        <is>
+          <t>근거 강도 정책 판</t>
+        </is>
+      </c>
+      <c r="X20" s="22" t="inlineStr">
+        <is>
+          <t>규칙 판</t>
+        </is>
+      </c>
+      <c r="Y20" s="22" t="inlineStr">
+        <is>
+          <t>근거 시각</t>
+        </is>
+      </c>
+      <c r="Z20" s="22" t="inlineStr">
+        <is>
+          <t>근거 시각 품질</t>
+        </is>
+      </c>
+      <c r="AA20" s="22" t="inlineStr">
+        <is>
+          <t>시간 신뢰도</t>
+        </is>
+      </c>
+      <c r="AB20" s="22" t="n"/>
+      <c r="AC20" s="22" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -18283,19 +19099,66 @@
       </c>
       <c r="P21" s="19" t="inlineStr">
         <is>
-          <t>verification_status</t>
+          <t>evidence_strength</t>
         </is>
       </c>
       <c r="Q21" s="19" t="inlineStr">
         <is>
-          <t>evidence_strength</t>
+          <t>value_status</t>
         </is>
       </c>
       <c r="R21" s="19" t="inlineStr">
         <is>
-          <t>confidence</t>
-        </is>
-      </c>
+          <t>verification_basis</t>
+        </is>
+      </c>
+      <c r="S21" s="19" t="inlineStr">
+        <is>
+          <t>freshness_status</t>
+        </is>
+      </c>
+      <c r="T21" s="19" t="inlineStr">
+        <is>
+          <t>conflict_status</t>
+        </is>
+      </c>
+      <c r="U21" s="19" t="inlineStr">
+        <is>
+          <t>hold_status</t>
+        </is>
+      </c>
+      <c r="V21" s="19" t="inlineStr">
+        <is>
+          <t>decision_usability</t>
+        </is>
+      </c>
+      <c r="W21" s="19" t="inlineStr">
+        <is>
+          <t>evidence_policy_version</t>
+        </is>
+      </c>
+      <c r="X21" s="19" t="inlineStr">
+        <is>
+          <t>rule_version</t>
+        </is>
+      </c>
+      <c r="Y21" s="19" t="inlineStr">
+        <is>
+          <t>evidence_time</t>
+        </is>
+      </c>
+      <c r="Z21" s="19" t="inlineStr">
+        <is>
+          <t>evidence_time_quality</t>
+        </is>
+      </c>
+      <c r="AA21" s="19" t="inlineStr">
+        <is>
+          <t>temporal_confidence</t>
+        </is>
+      </c>
+      <c r="AB21" s="19" t="n"/>
+      <c r="AC21" s="19" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -18385,9 +19248,56 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>DECIMAL(5,4)</t>
-        </is>
-      </c>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="U22" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="W22" s="6" t="inlineStr">
+        <is>
+          <t>STRING(20)</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr">
+        <is>
+          <t>STRING(20)</t>
+        </is>
+      </c>
+      <c r="Y22" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_TZ</t>
+        </is>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AA22" s="6" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="AB22" s="6" t="n"/>
+      <c r="AC22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -18467,19 +19377,66 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL / 당시 판정 사본</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL / 당시 판정 사본</t>
+          <t>NOT NULL / 당시 값 사본 / rev.2.3 신규</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
+          <t>NULL 허용 / 당시 값 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 당시 값 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 당시 값 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 당시 값 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 당시 값 사본 / 승인 가능 여부의 정본 / 네 차원 사본 + rule_version 사본 + 스냅샷 policy_version 으로 판정 재현 (I-27)</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 당시 판 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 당시 판 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 당시 값 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 당시 값 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 당시 값 사본 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="n"/>
+      <c r="AC23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
@@ -18512,20 +19469,20 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
           <t>EVT-000045</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
       <c r="M24" s="3" t="inlineStr">
         <is>
           <t>TEU</t>
@@ -18543,19 +19500,66 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>INFERRED</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>0.7000</t>
-        </is>
-      </c>
+          <t>HUMAN_VERIFICATION</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>FRESH</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>USABLE</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>ev-v1</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T08:20+09:00</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>SOURCE_EVENT_TIME</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="n"/>
+      <c r="AC24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
@@ -18598,14 +19602,14 @@
           <t>EVT-000077</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="inlineStr">
         <is>
           <t>KRW</t>
@@ -18616,22 +19620,61 @@
           <t>2026-09-18T00:00+09:00</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="n"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>FRESH</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>USABLE</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>ev-v1</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="n"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>SOURCE_EVENT_TIME</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="n"/>
+      <c r="AC25" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
@@ -27495,7 +28538,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>rev.2.2: 추출 결과(후보 값·인용·모델 판·프롬프트 판 등)는 불변. 검토 4컬럼(review_status·reviewed_by_actor_id·reviewed_at·created_event_id)만 PENDING -&gt; ACCEPTED/REJECTED/SUPERSEDED 한 방향 한 번. 신원·권한·근거 강도·상태 확정·숫자는 여기서 정하지 않는다 (ADR-026·029)</t>
+          <t>rev.2.2: 추출 결과(후보 값·인용·모델 판·프롬프트 판 등)는 불변. 검토 4컬럼(review_status·reviewed_by_actor_id·reviewed_at·created_event_id)만 PENDING -&gt; ACCEPTED/REJECTED/SUPERSEDED 한 방향 한 번. 신원·권한·근거 강도·상태 확정·숫자는 여기서 정하지 않는다 (ADR-026·029) / rev.2.3: docs/21 13절이 요구하는 스키마 판·입력 해시·검증기 결과를 보강했다. 불변 컬럼 12 -&gt; 15 (Markdown 15.9.2)</t>
         </is>
       </c>
     </row>
@@ -27585,6 +28628,21 @@
           <t>시뮬레이션</t>
         </is>
       </c>
+      <c r="R100" s="16" t="inlineStr">
+        <is>
+          <t>추출 스키마 판</t>
+        </is>
+      </c>
+      <c r="S100" s="16" t="inlineStr">
+        <is>
+          <t>입력 지문</t>
+        </is>
+      </c>
+      <c r="T100" s="16" t="inlineStr">
+        <is>
+          <t>검증기 결과</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -27672,6 +28730,21 @@
           <t>is_simulated</t>
         </is>
       </c>
+      <c r="R101" s="19" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="S101" s="19" t="inlineStr">
+        <is>
+          <t>input_hash</t>
+        </is>
+      </c>
+      <c r="T101" s="19" t="inlineStr">
+        <is>
+          <t>validator_result</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -27759,6 +28832,21 @@
           <t>BOOLEAN</t>
         </is>
       </c>
+      <c r="R102" s="6" t="inlineStr">
+        <is>
+          <t>STRING(20)</t>
+        </is>
+      </c>
+      <c r="S102" s="6" t="inlineStr">
+        <is>
+          <t>HASH</t>
+        </is>
+      </c>
+      <c r="T102" s="6" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -27846,6 +28934,21 @@
           <t>NOT NULL</t>
         </is>
       </c>
+      <c r="R103" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 어느 추출 계약으로 뽑았나 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="S103" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 무엇을 넣고 뽑았나 / rev.2.3 신규</t>
+        </is>
+      </c>
+      <c r="T103" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / docs/05 4.6 검사별 결과 / model_confidence 와 다르다 / rev.2.3 신규</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="21" t="inlineStr">
@@ -27931,6 +29034,21 @@
       <c r="Q104" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="R104" s="3" t="inlineStr">
+        <is>
+          <t>ex-1</t>
+        </is>
+      </c>
+      <c r="S104" s="3" t="inlineStr">
+        <is>
+          <t>(해시값)</t>
+        </is>
+      </c>
+      <c r="T104" s="3" t="inlineStr">
+        <is>
+          <t>[SCHEMA_OK, QUOTE_MATCHED]</t>
         </is>
       </c>
     </row>

--- a/docs/22_cera-logical-data-model.xlsx
+++ b/docs/22_cera-logical-data-model.xlsx
@@ -581,7 +581,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>rev.2.3 논리 모델 후속 T-081 DONE (2026-09-21, 사용자 최종 승인). docs/05 4.2 대조로 누락 13건 복구 + ADR-020 상태 차원 복구. 표 +1. 흐름 검증 47개 PASS</t>
+          <t>rev.2.4 Q-44 · Q-45 사용자 결정 반영 (2026-09-21). 메일 근거 시각 규칙 + 기록·내용 분리 보관. 표 수 변화 없음. 흐름 검증 64개 PASS. (rev.2.3 T-081 DONE 위)</t>
         </is>
       </c>
     </row>
@@ -3707,6 +3707,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="n">
         <v>2</v>
@@ -3782,7 +3783,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>사람의 결정은 plan_decision / message_approval / verification_request_handling 에 남는다. 감사는 그 위의 행위 기록</t>
+          <t>사람의 결정은 plan_decision / message_approval / verification_request_handling 에 남는다. 감사는 그 위의 행위 기록 / rev.2.4 (Q-45): 내용 파기도 감사한다 — action = CONTENT_PURGED, target_type = 내용 범주, target_id = 기록 id, request_context = 보관 정책 판, result. 파기한 내용은 여기에 복사하지 않는다 / 내용 부재는 성공한 CONTENT_PURGED 가 있을 때만 정상 파기. 감사 없는 부재는 데이터 손실(system_error). SUCCESS 는 제거 확인 뒤에만</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5137,7 +5138,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>[1] 사용자 결정 (6건 - D-1~D-5 2026-09-17, C 2026-09-21 전부 CLOSED)</t>
+          <t>[1] 사용자 결정 (8건 - D-1~D-5 2026-09-17, C · Q-44 · Q-45(구조) 2026-09-21 전부 CLOSED)</t>
         </is>
       </c>
     </row>
@@ -5365,631 +5366,651 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Q-44</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>메일 Date 헤더와 채널 수신 시각이 다를 때 source_recorded_at</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>① 대칭 허용 오차  ② 방향별(미래 Date 만 거부)  ③ 항상 internalDate  ④ 항상 Date  ⑤ 비움</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>CLOSED - ② (2026-09-21 사용자 결정)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Date 가 채널 수신 시각보다 미래가 아니면 Date. 늦게 도착한 메일을 최신처럼 만들지 않고, 미래 Date 위장을 막는다. 원래 두 시각은 event.payload</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>보통 - 두 시각을 보존했으므로 원문 파기 뒤에도 재판정 가능</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Q-45</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>실제 메일 보관·파기 정책</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>① 기록·내용 분리 + 단계적 파기  ② 무기한  ③ 원문 즉시 파기  ④ Pilot 까지 보류</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>구조 CLOSED - ① (2026-09-21 사용자 결정) / 기간 숫자 OPEN (Pilot 정책)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>행 삭제 ≠ 내용 파기. 내용은 참조 + 지문, 기록은 파기하지 않는다. 새 표 없음 (29절)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>구조: 어려움(처음부터 필요) / 기간 숫자: 쉬움 / 이미 파기한 내용: 되돌릴 수 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>[2] MVP 에서 만들지 않기로 한 테이블</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>영문 테이블명</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>한글</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>근거 항목</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>결정</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>근거</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>다시 여는 조건</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>exception_case</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>예외 운영 Case</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>E-36 · L-10 · D-5</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>CLOSED FOR MVP - 만들지 않는다</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Event -&gt; Risk -&gt; RecoveryRun -&gt; Communication -&gt; Reply -&gt; Re-run 폐쇄 루프에 필수가 아니다. 현재는 파생 조회</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>다시 여는 조건: 담당자 배정 · 예외 건 상태 · 종결 · SLA · Case 단위 협업. 만들 때는 결정적 case_key</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>operational_plan_batch</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>계획 업로드 묶음</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>E-35 · L-9 · D-4</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>CLOSED - 만들지 않는다</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>raw_input 1행이 이미 업로드 1건이고 그 배치의 plan.* 사건이 같은 raw_input_id 를 공유한다</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>다시 여는 조건: 배치 이름 · 상태 · 버전 · 승인 · 묶음 단위 되돌리기/교체</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>[3] 이번 단계에서 판정한 열린 질문</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>질문</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>스키마 반영</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>Q-54</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>외부 시스템 식별자 저장 구조</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>하이브리드</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>조회 경로 id 는 컬럼(comm_message/comm_thread), 화물·통관 id 는 external_identifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>Q-55</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>시설 하위 종류 구조</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>공통 + 1:1 상세</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>facility + facility_warehouse / facility_terminal / facility_odcy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>Q-58</t>
+          <t>Q-54</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>금액·통화 표현</t>
+          <t>외부 시스템 식별자 저장 구조</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>컬럼 묶음</t>
+          <t>하이브리드</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Money 테이블 없음. amount_krw + original_currency/amount + fx_rate + fx_rate_basis_date</t>
+          <t>조회 경로 id 는 컬럼(comm_message/comm_thread), 화물·통관 id 는 external_identifier</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>Q-59</t>
+          <t>Q-55</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>확인 요청 처리 기록의 참조 대상</t>
+          <t>시설 하위 종류 구조</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>결정적 request_key (DB FK 아님)</t>
+          <t>공통 + 1:1 상세</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>rev.2: DB 외래키가 아니라 논리 연결 키. 재료에서 conflict_id 같은 파생 대리키 제거</t>
+          <t>facility + facility_warehouse / facility_terminal / facility_odcy</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>Q-60</t>
+          <t>Q-58</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>CostLineItem 의 귀속</t>
+          <t>금액·통화 표현</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>필수 부모 1개 + 링크 테이블</t>
+          <t>컬럼 묶음</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>cost_result_id 만 NOT NULL. 귀속·근거는 cost_line_link(link_role)</t>
+          <t>Money 테이블 없음. amount_krw + original_currency/amount + fx_rate + fx_rate_basis_date</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>Q-62</t>
+          <t>Q-59</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Actor 구조</t>
+          <t>확인 요청 처리 기록의 참조 대상</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>최소 구성</t>
+          <t>결정적 request_key (DB FK 아님)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>actor_id / actor_type / display_name / is_active. 인증·권한은 나중</t>
+          <t>rev.2: DB 외래키가 아니라 논리 연결 키. 재료에서 conflict_id 같은 파생 대리키 제거</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>Q-63</t>
+          <t>Q-60</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>fact_key 분해</t>
+          <t>CostLineItem 의 귀속</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>원본은 문자열 유지</t>
+          <t>필수 부모 1개 + 링크 테이블</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>event.fact_key 는 불변 문자열. 파생 canonical_fact 에만 param_* 분해 컬럼</t>
+          <t>cost_result_id 만 NOT NULL. 귀속·근거는 cost_line_link(link_role)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>L-1</t>
+          <t>Q-62</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>회신 값을 원래 질문에 되붙이기</t>
+          <t>Actor 구조</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>질문 생성 시 대상 확정</t>
+          <t>최소 구성</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>question_item 이 target_entity_type/id · target_fact_key · target_applicability_scope_type/ref(rev.2.1) 를 질문 생성 시 확정하고 ask_id 로 단건 조회. 개체·사실 키·적용 범위가 모두 그 행에서 나오며 LLM 은 범위를 만지지 않는다</t>
+          <t>actor_id / actor_type / display_name / is_active. 인증·권한은 나중</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>L-2</t>
+          <t>Q-63</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Container ↔ B/L</t>
+          <t>fact_key 분해</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>연결 테이블</t>
+          <t>원본은 문자열 유지</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>container_bl + PRIMARY 부분 유일 제약 (D-1 CLOSED)</t>
+          <t>event.fact_key 는 불변 문자열. 파생 canonical_fact 에만 param_* 분해 컬럼</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>L-3</t>
+          <t>L-1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>제안 묶음</t>
+          <t>회신 값을 원래 질문에 되붙이기</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>테이블로 만든다</t>
+          <t>질문 생성 시 대상 확정</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>commercial_offer + item, 분류 EVIDENCE (D-2 CLOSED)</t>
+          <t>question_item 이 target_entity_type/id · target_fact_key · target_applicability_scope_type/ref(rev.2.1) 를 질문 생성 시 확정하고 ask_id 로 단건 조회. 개체·사실 키·적용 범위가 모두 그 행에서 나오며 LLM 은 범위를 만지지 않는다</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>L-3b</t>
+          <t>L-2</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>운영자 입력 요율의 적용 대상·기간</t>
+          <t>Container ↔ B/L</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>범위와 기간을 분리</t>
+          <t>연결 테이블</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>rev.2: valid_from/until(시간) 과 applicability_scope_type/ref(대상) 을 다른 축으로. 기본 RECOVERY_CONTEXT</t>
+          <t>container_bl + PRIMARY 부분 유일 제약 (D-1 CLOSED)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>L-4</t>
+          <t>L-3</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>마스터 값 vs 사실</t>
+          <t>제안 묶음</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>default_ 접두</t>
+          <t>테이블로 만든다</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>마스터에는 평시 기준선만. 그날 값은 사실이 이긴다. 계산에 쓴 기본값은 스냅샷에 얼린다</t>
+          <t>commercial_offer + item, 분류 EVIDENCE (D-2 CLOSED)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>L-5</t>
+          <t>L-3b</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>차량 표현</t>
+          <t>운영자 입력 요율의 적용 대상·기간</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>풀 단위</t>
+          <t>범위와 기간을 분리</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>plan.truck_pool / plan.depart_slot 사실. 개별 차량 없음</t>
+          <t>rev.2: valid_from/until(시간) 과 applicability_scope_type/ref(대상) 을 다른 축으로. 기본 RECOVERY_CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>L-6</t>
+          <t>L-4</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>예외 처리 단위</t>
+          <t>마스터 값 vs 사실</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>L-10 으로 합침</t>
+          <t>default_ 접두</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>D-5 CLOSED FOR MVP</t>
+          <t>마스터에는 평시 기준선만. 그날 값은 사실이 이긴다. 계산에 쓴 기본값은 스냅샷에 얼린다</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>L-7</t>
+          <t>L-5</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>발송 시도</t>
+          <t>차량 표현</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>별도 테이블</t>
+          <t>풀 단위</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>send_attempt. rev.2: 승인은 메시지 종류에 따른 조건부 필수</t>
+          <t>plan.truck_pool / plan.depart_slot 사실. 개별 차량 없음</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>L-8</t>
+          <t>L-6</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>시뮬레이션 분리</t>
+          <t>예외 처리 단위</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>같은 테이블 + 플래그</t>
+          <t>L-10 으로 합침</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>is_simulated + scenario_id, 산출물은 contains_simulated 로 전파</t>
+          <t>D-5 CLOSED FOR MVP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>L-9</t>
+          <t>L-7</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>계획 업로드 묶음</t>
+          <t>발송 시도</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>만들지 않는다</t>
+          <t>별도 테이블</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>raw_input 이 배치 출처 (D-4 CLOSED)</t>
+          <t>send_attempt. rev.2: 승인은 메시지 종류에 따른 조건부 필수</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-8</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ExceptionCase</t>
+          <t>시뮬레이션 분리</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>MVP 에서 만들지 않는다</t>
+          <t>같은 테이블 + 플래그</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>파생 조회 (D-5 CLOSED FOR MVP)</t>
+          <t>is_simulated + scenario_id, 산출물은 contains_simulated 로 전파</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-9</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>MessageApproval</t>
+          <t>계획 업로드 묶음</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>덧붙이기 + 승인 사본 + 무효화 행</t>
+          <t>만들지 않는다</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>rev.2: 구조화 값까지 얼리고, 취소·만료·계획 교체를 UPDATE 없이 남긴다</t>
+          <t>raw_input 이 배치 출처 (D-4 CLOSED)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>운영자 계획 조건</t>
+          <t>ExceptionCase</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>별도 DECISION_RECORD 테이블</t>
+          <t>MVP 에서 만들지 않는다</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>rev.2: 해제도 action=RELEASE 새 행. 기본 범위는 RECOVERY_CONTEXT. 솔버 표현은 미확정</t>
+          <t>파생 조회 (D-5 CLOSED FOR MVP)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>L-13</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>복구 맥락(Recovery Context)의 식별자</t>
+          <t>MessageApproval</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>OPEN - rev.2 신규</t>
+          <t>덧붙이기 + 승인 사본 + 무효화 행</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>후보: recovery_run 계보의 뿌리 / 최초 계기 사건 / 컨테이너 집합 지문. T-069 에서 답한다</t>
+          <t>rev.2: 구조화 값까지 얼리고, 취소·만료·계획 교체를 UPDATE 없이 남긴다</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>L-14</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>적용 범위의 값 목록 + 범위 선택 정책</t>
+          <t>운영자 계획 조건</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>OPEN - rev.2 신규 / rev.2.1 확장</t>
+          <t>별도 DECISION_RECORD 테이블</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>① 값 목록 enum 미확정 (기본값이 RECOVERY_CONTEXT 라는 것만 확정) ② 여러 범위가 동시에 적용 가능할 때의 선택 정책도 확정하지 않는다 - CONTRACT/CONTAINER/RECOVERY_CONTEXT 는 서로 다른 축이라 한 줄로 못 세운다. 확정한 것: 범위는 사실 식별자에 포함 · 같은 범위끼리만 Reconciliation · 결정론적 선택 정책이 필요함 · 쓴 범위는 스냅샷에 남음</t>
+          <t>rev.2: 해제도 action=RELEASE 새 행. 기본 범위는 RECOVERY_CONTEXT. 솔버 표현은 미확정</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>L-15</t>
+          <t>L-13</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>message_kind 값 목록</t>
+          <t>복구 맥락(Recovery Context)의 식별자</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -5999,228 +6020,279 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>지금은 BUSINESS / CONTACT_VERIFICATION 둘만. 늘리는 것은 쉽다</t>
+          <t>후보: recovery_run 계보의 뿌리 / 최초 계기 사건 / 컨테이너 집합 지문. T-069 에서 답한다</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>L-16</t>
+          <t>L-14</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>bl 의 업무 유일 제약</t>
+          <t>적용 범위의 값 목록 + 범위 선택 정책</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>OPEN - rev.2 신규</t>
+          <t>OPEN - rev.2 신규 / rev.2.1 확장</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>(bl_type, bl_no, bl_year) 는 후보일 뿐. 번호가 연도 안에서 유일한지 미확인. 실데이터 확인 뒤 물리 설계</t>
+          <t>① 값 목록 enum 미확정 (기본값이 RECOVERY_CONTEXT 라는 것만 확정) ② 여러 범위가 동시에 적용 가능할 때의 선택 정책도 확정하지 않는다 - CONTRACT/CONTAINER/RECOVERY_CONTEXT 는 서로 다른 축이라 한 줄로 못 세운다. 확정한 것: 범위는 사실 식별자에 포함 · 같은 범위끼리만 Reconciliation · 결정론적 선택 정책이 필요함 · 쓴 범위는 스냅샷에 남음</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
+          <t>L-15</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>message_kind 값 목록</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>OPEN - rev.2 신규</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>지금은 BUSINESS / CONTACT_VERIFICATION 둘만. 늘리는 것은 쉽다</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>L-16</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>bl 의 업무 유일 제약</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>OPEN - rev.2 신규</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>(bl_type, bl_no, bl_year) 는 후보일 뿐. 번호가 연도 안에서 유일한지 미확인. 실데이터 확인 뒤 물리 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
           <t>Q-66</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>system_error 의 오류 분류·코드 값 목록</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>OPEN - rev.2.2 신규</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>예시(GMAIL_TIMEOUT · GMAIL_RATE_LIMITED · GMAIL_AUTH_EXPIRED · EXTERNAL_RESPONSE_INVALID)만 적었다. 전체 목록은 T-069 구현 계획·구현에서 정한다 (docs/23 6절)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Q-46</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>상대방이 직접 입력한 구조화 값의 Source 모델</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>OPEN - 유지 (rev.2.3 에서 닫지 않았다)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>source_type 7값은 현재 ADR-020 기준의 정렬이지 영구 확정 enum 이 아니다. HUMAN_UI 로 넣으면 거래처 입력이 CERA 사용자 입력과 같은 강도가 되어 권한 모델이 무너진다. actor_type 축 신설 여부는 권한 모델과 함께 정한다</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Q-34</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>event.payload.change_reason 의 값 목록</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>OPEN - rev.2.3 신규</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>R6 변화 선언 예외 판정의 입력. 값 목록은 T-037 · 인터뷰</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="23" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>[4] 이번 단계에서 정하지 않는 것</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>DB 제품 (PostgreSQL / MySQL / SQLite)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>ORM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>실제 CREATE TABLE SQL / 마이그레이션</t>
+          <t>DB 제품 (PostgreSQL / MySQL / SQLite)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>인덱스·파티션·복제</t>
+          <t>ORM</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>API endpoint</t>
+          <t>실제 CREATE TABLE SQL / 마이그레이션</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>LLM 공급자·모델</t>
+          <t>인덱스·파티션·복제</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>솔버와 그 내부 표현</t>
+          <t>API endpoint</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>위험·신선도·근거 강도의 실제 임계값</t>
+          <t>LLM 공급자·모델</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>plan_decision.decision_type 의 값 목록</t>
+          <t>솔버와 그 내부 표현</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>applicability_scope_type 값 목록 (L-14)</t>
+          <t>위험·신선도·근거 강도의 실제 임계값</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>복구 맥락 식별자 (L-13)</t>
+          <t>plan_decision.decision_type 의 값 목록</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>bl 의 실제 UNIQUE 제약 (L-16)</t>
+          <t>applicability_scope_type 값 목록 (L-14)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>적용 범위 사이의 우선순위 규칙 (L-14)</t>
+          <t>복구 맥락 식별자 (L-13)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>system_error 오류 분류·코드 값 목록 (Q-66)</t>
+          <t>bl 의 실제 UNIQUE 제약 (L-16)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Backend 언어·프레임워크 (ADR-031 Proposed, docs/23)</t>
+          <t>적용 범위 사이의 우선순위 규칙 (L-14)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>event.idempotency_key 의 직렬화·해시 알고리즘·주장 위치(claim locator) 형식 (11.2d)</t>
+          <t>system_error 오류 분류·코드 값 목록 (Q-66)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>event.schema_version 문자열 형식</t>
+          <t>Backend 언어·프레임워크 (ADR-031 Proposed, docs/23)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>event.idempotency_key 의 직렬화·해시 알고리즘·주장 위치(claim locator) 형식 (11.2d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>event.schema_version 문자열 형식</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
           <t>input_confidence_reasons / validator_result 의 JSON 구조 세부</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>실제 메일 보관 기간 숫자 (Q-45 기간 - Pilot 정책) / 보관 관리 내용의 물리 저장 위치</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11541,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>rev.2: payload_hash UNIQUE 제거. 내용이 같아도 재수집은 새 관측이다 (예시 1·2 는 같은 해시). 중복 처리 차단은 출처가 주는 source_record_key 로만 한다 / rev.2.3: source_type 값을 ADR-020 7값으로 맞췄다 (event.source_type 과 같은 집합)</t>
+          <t>rev.2: payload_hash UNIQUE 제거. 내용이 같아도 재수집은 새 관측이다 (예시 1·2 는 같은 해시). 중복 처리 차단은 출처가 주는 source_record_key 로만 한다 / rev.2.3: source_type 값을 ADR-020 7값으로 맞췄다 (event.source_type 과 같은 집합) / rev.2.4 (Q-45): 원문은 보관 관리 내용. 보관 기간이 끝나면 원문만 파기되고 이 행·지문·외부 id·시각은 남는다. source_recorded_at 은 메일이면 Q-44 규칙(Date 가 채널 수신 시각보다 미래가 아니면 Date)</t>
         </is>
       </c>
     </row>
@@ -11511,25 +11583,30 @@
       </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
+          <t>첨부 목록</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
           <t>출처 전달 키</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>출처 기록 시각</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>수신 시각</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t>수집 주체</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="M11" s="16" t="inlineStr">
         <is>
           <t>시뮬레이션</t>
         </is>
@@ -11561,7 +11638,7 @@
           <t>request_ref</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>payload_ref</t>
         </is>
@@ -11571,27 +11648,32 @@
           <t>payload_hash</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>attachment_manifest</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>source_record_key</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>source_recorded_at</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>received_at</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>collected_by_actor_id</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t>is_simulated</t>
         </is>
@@ -11635,25 +11717,30 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
           <t>STRING(200)</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>REF(actor)</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
@@ -11687,35 +11774,40 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
+          <t>NULL 허용 / 보관 관리 내용 참조(29절). 파기돼도 참조는 남는다 / rev.2.4</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / UNIQUE 아님</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 첨부마다 지문·크기·형식만. 파일명·내용 금지 / rev.2.4 신규</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>출처가 줄 때만 / 있을 때 유일</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / UNIQUE 아님</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>출처가 줄 때만 / 있을 때 유일</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -11747,33 +11839,30 @@
           <t>blYy=2026&amp;blNo=* (마스킹)</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>store://raw/000001</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
           <t>(해시값)</t>
         </is>
       </c>
       <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T06:00+09:00</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T06:00+09:00</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>ACT-SYS-01</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -11805,33 +11894,30 @@
           <t>blYy=2026&amp;blNo=* (마스킹)</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>store://raw/000003</t>
-        </is>
-      </c>
+      <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>(같은 해시값)</t>
         </is>
       </c>
       <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T10:00+09:00</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T10:00+09:00</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>ACT-SYS-01</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -11859,37 +11945,34 @@
         </is>
       </c>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>store://raw/000009</t>
-        </is>
-      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>(해시값)</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>mock-msg-0021</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T10:30+09:00</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T10:30+09:00</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>ACT-SYS-01</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -17491,7 +17574,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>계산에 들어가려면 사건이 되어 사실로 채택되어야 한다</t>
+          <t>계산에 들어가려면 사건이 되어 사실로 채택되어야 한다 / rev.2.4 (Q-45): 조건 원문은 보관 관리 내용. 계산에 쓰는 값은 commercial_offer_item</t>
         </is>
       </c>
     </row>
@@ -17548,20 +17631,25 @@
       </c>
       <c r="K30" s="16" t="inlineStr">
         <is>
-          <t>조건 원문</t>
+          <t>조건 원문 참조</t>
         </is>
       </c>
       <c r="L30" s="16" t="inlineStr">
         <is>
+          <t>조건 원문 지문</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="M30" s="16" t="inlineStr">
+      <c r="N30" s="16" t="inlineStr">
         <is>
           <t>시뮬레이션</t>
         </is>
       </c>
-      <c r="N30" s="16" t="inlineStr">
+      <c r="O30" s="16" t="inlineStr">
         <is>
           <t>시나리오</t>
         </is>
@@ -17620,20 +17708,25 @@
       </c>
       <c r="K31" s="19" t="inlineStr">
         <is>
-          <t>conditions_text</t>
+          <t>conditions_content_ref</t>
         </is>
       </c>
       <c r="L31" s="19" t="inlineStr">
         <is>
+          <t>conditions_hash</t>
+        </is>
+      </c>
+      <c r="M31" s="19" t="inlineStr">
+        <is>
           <t>offer_status</t>
         </is>
       </c>
-      <c r="M31" s="19" t="inlineStr">
+      <c r="N31" s="19" t="inlineStr">
         <is>
           <t>is_simulated</t>
         </is>
       </c>
-      <c r="N31" s="20" t="inlineStr">
+      <c r="O31" s="20" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
@@ -17692,20 +17785,25 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>STRING(300)</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
+          <t>HASH</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="N32" s="6" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="N32" s="6" t="inlineStr">
+      <c r="O32" s="6" t="inlineStr">
         <is>
           <t>REF(scenario)</t>
         </is>
@@ -17764,20 +17862,25 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용</t>
+          <t>NULL 허용 / 보관 관리 내용 참조(29절). 파기돼도 참조는 남는다 / rev.2.4 (옛 conditions_text)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
+          <t>참조가 있으면 NOT NULL / 파기돼도 남는다 / rev.2.4 신규</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
           <t>RECEIVED / SUPERSEDED / EXPIRED / WITHDRAWN</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
@@ -17809,7 +17912,7 @@
           <t>MSG-000021</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
           <t>QI-0002</t>
@@ -17830,22 +17933,19 @@
           <t>2026-09-20T23:59+09:00</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>주말 반입 불가 (예시)</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>RECEIVED</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
@@ -25509,7 +25609,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>rev.2: message_kind 신규. CONTACT_VERIFICATION 은 업무 발송 승인의 예외지만 구조화 값·질문 연결을 가질 수 없고 감사는 남는다. 실제 메일 본문은 커밋하지 않는다 (docs/01 6절)</t>
+          <t>rev.2: message_kind 신규. CONTACT_VERIFICATION 은 업무 발송 승인의 예외지만 구조화 값·질문 연결을 가질 수 없고 감사는 남는다. 실제 메일 본문은 커밋하지 않는다 (docs/01 6절) / rev.2.4 (Q-45): 제목·본문은 보관 관리 내용. content_hash 는 파기돼도 남아 승인·발송 대조에 쓰인다. 원본 HTML 은 저장하지 않는다</t>
         </is>
       </c>
     </row>
@@ -25566,59 +25666,55 @@
       </c>
       <c r="K30" s="16" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>제목·본문 참조</t>
         </is>
       </c>
       <c r="L30" s="16" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>본문 지문</t>
         </is>
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>본문 지문</t>
+          <t>현재 상태</t>
         </is>
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>현재 상태</t>
+          <t>현재 승인</t>
         </is>
       </c>
       <c r="O30" s="16" t="inlineStr">
         <is>
-          <t>현재 승인</t>
+          <t>작성 주체</t>
         </is>
       </c>
       <c r="P30" s="16" t="inlineStr">
         <is>
-          <t>작성 주체</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="Q30" s="16" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>발송 시각</t>
         </is>
       </c>
       <c r="R30" s="16" t="inlineStr">
         <is>
-          <t>발송 시각</t>
+          <t>수신 시각</t>
         </is>
       </c>
       <c r="S30" s="16" t="inlineStr">
         <is>
-          <t>수신 시각</t>
+          <t>시뮬레이션</t>
         </is>
       </c>
       <c r="T30" s="16" t="inlineStr">
         <is>
-          <t>시뮬레이션</t>
-        </is>
-      </c>
-      <c r="U30" s="16" t="inlineStr">
-        <is>
           <t>시나리오</t>
         </is>
       </c>
+      <c r="U30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -25673,59 +25769,55 @@
       </c>
       <c r="K31" s="19" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>message_content_ref</t>
         </is>
       </c>
       <c r="L31" s="19" t="inlineStr">
         <is>
-          <t>body_text</t>
+          <t>content_hash</t>
         </is>
       </c>
       <c r="M31" s="19" t="inlineStr">
         <is>
-          <t>content_hash</t>
-        </is>
-      </c>
-      <c r="N31" s="19" t="inlineStr">
-        <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="O31" s="20" t="inlineStr">
+      <c r="N31" s="20" t="inlineStr">
         <is>
           <t>current_approval_id</t>
         </is>
       </c>
+      <c r="O31" s="19" t="inlineStr">
+        <is>
+          <t>drafted_by</t>
+        </is>
+      </c>
       <c r="P31" s="19" t="inlineStr">
         <is>
-          <t>drafted_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>sent_at</t>
         </is>
       </c>
       <c r="R31" s="19" t="inlineStr">
         <is>
-          <t>sent_at</t>
+          <t>received_at</t>
         </is>
       </c>
       <c r="S31" s="19" t="inlineStr">
         <is>
-          <t>received_at</t>
-        </is>
-      </c>
-      <c r="T31" s="19" t="inlineStr">
-        <is>
           <t>is_simulated</t>
         </is>
       </c>
-      <c r="U31" s="20" t="inlineStr">
+      <c r="T31" s="20" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
+      <c r="U31" s="20" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -25785,27 +25877,27 @@
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>HASH</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>HASH</t>
+          <t>CODE</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
+          <t>REF(message_approval)</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>REF(message_approval)</t>
-        </is>
-      </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>CODE</t>
+          <t>TIMESTAMP_TZ</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
@@ -25820,19 +25912,15 @@
       </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
-          <t>TIMESTAMP_TZ</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
           <t>REF(scenario)</t>
         </is>
       </c>
+      <c r="U32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -25887,59 +25975,55 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
+          <t>NULL 허용 / 제목 + 안전한 텍스트 본문 한 묶음. 보관 관리 내용 참조(29절). 파기돼도 참조는 남는다 / rev.2.4 (옛 subject · body_text)</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 수신자+제목+본문+구조화 값을 덮는다</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 캐시</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 편의 포인터</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>AI_DRAFT / HUMAN / TEMPLATE</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / AI 는 문장만 쓴다</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 수신자+제목+본문+구조화 값을 덮는다</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL / 캐시</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 편의 포인터</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>AI_DRAFT / HUMAN / TEMPLATE</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="T33" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
+      <c r="U33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
@@ -25967,7 +26051,7 @@
           <t>BUSINESS</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
           <t>MOCK</t>
@@ -25988,53 +26072,45 @@
           <t>AD-0002</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>9/18 입고 가능 수량 문의 (예시)</t>
-        </is>
-      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>(본문 - 합성)</t>
+          <t>(해시값)</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>(해시값)</t>
+          <t>SENT</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>SENT</t>
+          <t>APV-0001</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>APV-0001</t>
+          <t>AI_DRAFT</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>AI_DRAFT</t>
+          <t>2026-09-18T09:10+09:00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18T09:10+09:00</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
           <t>2026-09-18T09:12+09:00</t>
         </is>
       </c>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr">
+      <c r="R34" s="3" t="n"/>
+      <c r="S34" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="U34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="n"/>
+      <c r="U34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
@@ -26062,7 +26138,7 @@
           <t>BUSINESS</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>MOCK</t>
@@ -26078,50 +26154,42 @@
           <t>odcy@example.invalid</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>RE: 요율 문의 (예시)</t>
-        </is>
-      </c>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>(본문 - 합성)</t>
+          <t>(해시값)</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>(해시값)</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
           <t>REPLIED</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>HUMAN</t>
+        </is>
+      </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>HUMAN</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
           <t>2026-09-18T10:30+09:00</t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="n"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18T10:30+09:00</t>
+        </is>
+      </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18T10:30+09:00</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="U35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="n"/>
+      <c r="U35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
@@ -26174,30 +26242,26 @@
           <t>AD-0001</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>주소 확인 안내 (예시)</t>
-        </is>
-      </c>
+      <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>(토큰 링크만 - 합성)</t>
+          <t>(해시값)</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>(해시값)</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
           <t>SENT</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>2026-09-16T09:50+09:00</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -26205,18 +26269,14 @@
           <t>2026-09-16T09:50+09:00</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16T09:50+09:00</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr">
+      <c r="R36" s="3" t="n"/>
+      <c r="S36" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="n"/>
+      <c r="U36" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
@@ -26806,7 +26866,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>rev.2.1·rev.2.2: 행 종류별 필수 컬럼이 다르다. APPROVED = approved_content_hash · approved_to_address_id 필수 + 메시지에 값이 있는 범위에서 제목·본문·구조화 값 사본 필수. REJECTED/REVISION_REQUESTED = reason 필수, 사본 조건을 적용하지 않는다. REVOKED/INVALIDATED = invalidates_approval_id + invalidation_cause 필수, 새 지문·사본 불필요, 대상은 같은 message_id 의 기존 APPROVED. 만료는 expires_at(만들 때 정함). 어떤 행도 UPDATE 하지 않는다</t>
+          <t>rev.2.1·rev.2.2: 행 종류별 필수 컬럼이 다르다. APPROVED = approved_content_hash · approved_to_address_id 필수 + 메시지에 값이 있는 범위에서 제목·본문·구조화 값 사본 필수. REJECTED/REVISION_REQUESTED = reason 필수, 사본 조건을 적용하지 않는다. REVOKED/INVALIDATED = invalidates_approval_id + invalidation_cause 필수, 새 지문·사본 불필요, 대상은 같은 message_id 의 기존 APPROVED. 만료는 expires_at(만들 때 정함). 어떤 행도 UPDATE 하지 않는다 / rev.2.4 (Q-45): 승인 문장 사본은 보관 관리 내용. approved_content_hash 와 승인·무효화 사슬은 기록으로 남는다. 유효한 승인의 사본은 파기하지 않는다</t>
         </is>
       </c>
     </row>
@@ -26858,34 +26918,30 @@
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>승인 시점 제목</t>
+          <t>승인 제목·본문 참조</t>
         </is>
       </c>
       <c r="K60" s="16" t="inlineStr">
         <is>
-          <t>승인 시점 본문</t>
+          <t>승인 시점 계획</t>
         </is>
       </c>
       <c r="L60" s="16" t="inlineStr">
         <is>
-          <t>승인 시점 계획</t>
+          <t>승인 내용 지문</t>
         </is>
       </c>
       <c r="M60" s="16" t="inlineStr">
         <is>
-          <t>승인 내용 지문</t>
+          <t>승인 시점 수신자</t>
         </is>
       </c>
       <c r="N60" s="16" t="inlineStr">
         <is>
-          <t>승인 시점 수신자</t>
-        </is>
-      </c>
-      <c r="O60" s="16" t="inlineStr">
-        <is>
           <t>사유</t>
         </is>
       </c>
+      <c r="O60" s="16" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -26935,34 +26991,30 @@
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t>approved_subject</t>
-        </is>
-      </c>
-      <c r="K61" s="19" t="inlineStr">
-        <is>
-          <t>approved_body_text</t>
-        </is>
-      </c>
-      <c r="L61" s="20" t="inlineStr">
+          <t>approved_content_ref</t>
+        </is>
+      </c>
+      <c r="K61" s="20" t="inlineStr">
         <is>
           <t>approved_plan_run_id</t>
         </is>
       </c>
-      <c r="M61" s="19" t="inlineStr">
+      <c r="L61" s="19" t="inlineStr">
         <is>
           <t>approved_content_hash</t>
         </is>
       </c>
-      <c r="N61" s="20" t="inlineStr">
+      <c r="M61" s="20" t="inlineStr">
         <is>
           <t>approved_to_address_id</t>
         </is>
       </c>
-      <c r="O61" s="19" t="inlineStr">
+      <c r="N61" s="19" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
+      <c r="O61" s="19" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -27017,29 +27069,25 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REF(recovery_run)</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>REF(recovery_run)</t>
+          <t>HASH</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
-          <t>HASH</t>
+          <t>REF(contact_channel_address)</t>
         </is>
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>REF(contact_channel_address)</t>
-        </is>
-      </c>
-      <c r="O62" s="6" t="inlineStr">
-        <is>
           <t>STRING(500)</t>
         </is>
       </c>
+      <c r="O62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -27089,34 +27137,30 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>APPROVED 이고 원 메시지에 값이 있으면 필수 / 사본 (값이 없는 메시지에 빈 사본을 요구하지 않는다)</t>
+          <t>조건부 - APPROVED 이고 메시지에 제목·본문이 있으면 NOT NULL / 보관 관리 내용 참조(29절). 파기돼도 참조는 남는다 / rev.2.4</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>APPROVED 이고 원 메시지에 값이 있으면 필수 / 사본 (값이 없는 메시지에 빈 사본을 요구하지 않는다)</t>
+          <t>NULL 허용 / 계획 기반 메시지의 APPROVED 면 필수</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용 / 계획 기반 메시지의 APPROVED 면 필수</t>
+          <t>APPROVED 면 필수 / REVOKED·INVALIDATED 는 불필요 / 구조화 값까지 덮는다</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>APPROVED 면 필수 / REVOKED·INVALIDATED 는 불필요 / 구조화 값까지 덮는다</t>
+          <t>APPROVED 면 필수</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>APPROVED 면 필수</t>
-        </is>
-      </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
           <t>REJECTED·REVISION_REQUESTED 면 필수 / 무효화일 때 권장</t>
         </is>
       </c>
+      <c r="O63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
@@ -27139,8 +27183,8 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
           <t>ACT-USR-01</t>
@@ -27156,32 +27200,24 @@
           <t>2026-09-18T17:00+09:00</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>9/18 입고 가능 수량 문의 (예시)</t>
-        </is>
-      </c>
+      <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>(승인 당시 본문 - 합성)</t>
+          <t>RUN-0001</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>RUN-0001</t>
+          <t>(해시값)</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>(해시값)</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="inlineStr">
-        <is>
           <t>AD-0002</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="n"/>
+      <c r="O64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
@@ -27224,25 +27260,25 @@
           <t>2026-09-18T10:21+09:00</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr"/>
-      <c r="K65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>RUN-0002</t>
+        </is>
+      </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>RUN-0002</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
           <t>(해시값)</t>
         </is>
       </c>
-      <c r="N65" s="3" t="inlineStr"/>
-      <c r="O65" s="3" t="inlineStr">
+      <c r="M65" s="3" t="n"/>
+      <c r="N65" s="3" t="inlineStr">
         <is>
           <t>계획이 RUN-0002 로 교체됨 (예시)</t>
         </is>
       </c>
+      <c r="O65" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -28538,7 +28574,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>rev.2.2: 추출 결과(후보 값·인용·모델 판·프롬프트 판 등)는 불변. 검토 4컬럼(review_status·reviewed_by_actor_id·reviewed_at·created_event_id)만 PENDING -&gt; ACCEPTED/REJECTED/SUPERSEDED 한 방향 한 번. 신원·권한·근거 강도·상태 확정·숫자는 여기서 정하지 않는다 (ADR-026·029) / rev.2.3: docs/21 13절이 요구하는 스키마 판·입력 해시·검증기 결과를 보강했다. 불변 컬럼 12 -&gt; 15 (Markdown 15.9.2)</t>
+          <t>rev.2.2: 추출 결과(후보 값·인용·모델 판·프롬프트 판 등)는 불변. 검토 4컬럼(review_status·reviewed_by_actor_id·reviewed_at·created_event_id)만 PENDING -&gt; ACCEPTED/REJECTED/SUPERSEDED 한 방향 한 번. 신원·권한·근거 강도·상태 확정·숫자는 여기서 정하지 않는다 (ADR-026·029) / rev.2.3: docs/21 13절이 요구하는 스키마 판·입력 해시·검증기 결과를 보강했다. 불변 컬럼 12 -&gt; 15 (Markdown 15.9.2) / rev.2.4 (Q-45): 인용은 원문의 일부라 보관 관리 내용(원문보다 오래 둘 수 있다). 불변 컬럼 16. PENDING 이거나 열린 확인 요청의 근거면 파기하지 않는다</t>
         </is>
       </c>
     </row>
@@ -28580,65 +28616,70 @@
       </c>
       <c r="H100" s="16" t="inlineStr">
         <is>
-          <t>근거 인용</t>
+          <t>근거 인용 참조</t>
         </is>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
+          <t>근거 인용 지문</t>
+        </is>
+      </c>
+      <c r="J100" s="16" t="inlineStr">
+        <is>
           <t>인용 위치</t>
         </is>
       </c>
-      <c r="J100" s="16" t="inlineStr">
+      <c r="K100" s="16" t="inlineStr">
         <is>
           <t>모델 판</t>
         </is>
       </c>
-      <c r="K100" s="16" t="inlineStr">
+      <c r="L100" s="16" t="inlineStr">
         <is>
           <t>프롬프트 판</t>
         </is>
       </c>
-      <c r="L100" s="16" t="inlineStr">
+      <c r="M100" s="16" t="inlineStr">
         <is>
           <t>모델 자기 점수</t>
         </is>
       </c>
-      <c r="M100" s="16" t="inlineStr">
+      <c r="N100" s="16" t="inlineStr">
         <is>
           <t>처리 상태</t>
         </is>
       </c>
-      <c r="N100" s="16" t="inlineStr">
+      <c r="O100" s="16" t="inlineStr">
         <is>
           <t>채택 주체</t>
         </is>
       </c>
-      <c r="O100" s="16" t="inlineStr">
+      <c r="P100" s="16" t="inlineStr">
         <is>
           <t>채택 시각</t>
         </is>
       </c>
-      <c r="P100" s="16" t="inlineStr">
+      <c r="Q100" s="16" t="inlineStr">
         <is>
           <t>생성 사건</t>
         </is>
       </c>
-      <c r="Q100" s="16" t="inlineStr">
+      <c r="R100" s="16" t="inlineStr">
         <is>
           <t>시뮬레이션</t>
         </is>
       </c>
-      <c r="R100" s="16" t="inlineStr">
+      <c r="S100" s="16" t="inlineStr">
         <is>
           <t>추출 스키마 판</t>
         </is>
       </c>
-      <c r="S100" s="16" t="inlineStr">
+      <c r="T100" s="16" t="inlineStr">
         <is>
           <t>입력 지문</t>
         </is>
       </c>
-      <c r="T100" s="16" t="inlineStr">
+      <c r="U100" s="16" t="inlineStr">
         <is>
           <t>검증기 결과</t>
         </is>
@@ -28682,65 +28723,70 @@
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t>source_quote</t>
+          <t>source_quote_ref</t>
         </is>
       </c>
       <c r="I101" s="19" t="inlineStr">
         <is>
+          <t>source_quote_hash</t>
+        </is>
+      </c>
+      <c r="J101" s="19" t="inlineStr">
+        <is>
           <t>quote_location</t>
         </is>
       </c>
-      <c r="J101" s="19" t="inlineStr">
+      <c r="K101" s="19" t="inlineStr">
         <is>
           <t>model_version</t>
         </is>
       </c>
-      <c r="K101" s="19" t="inlineStr">
+      <c r="L101" s="19" t="inlineStr">
         <is>
           <t>prompt_version</t>
         </is>
       </c>
-      <c r="L101" s="19" t="inlineStr">
+      <c r="M101" s="19" t="inlineStr">
         <is>
           <t>model_confidence</t>
         </is>
       </c>
-      <c r="M101" s="19" t="inlineStr">
+      <c r="N101" s="19" t="inlineStr">
         <is>
           <t>review_status</t>
         </is>
       </c>
-      <c r="N101" s="20" t="inlineStr">
+      <c r="O101" s="20" t="inlineStr">
         <is>
           <t>reviewed_by_actor_id</t>
         </is>
       </c>
-      <c r="O101" s="19" t="inlineStr">
+      <c r="P101" s="19" t="inlineStr">
         <is>
           <t>reviewed_at</t>
         </is>
       </c>
-      <c r="P101" s="20" t="inlineStr">
+      <c r="Q101" s="20" t="inlineStr">
         <is>
           <t>created_event_id</t>
         </is>
       </c>
-      <c r="Q101" s="19" t="inlineStr">
+      <c r="R101" s="19" t="inlineStr">
         <is>
           <t>is_simulated</t>
         </is>
       </c>
-      <c r="R101" s="19" t="inlineStr">
+      <c r="S101" s="19" t="inlineStr">
         <is>
           <t>schema_version</t>
         </is>
       </c>
-      <c r="S101" s="19" t="inlineStr">
+      <c r="T101" s="19" t="inlineStr">
         <is>
           <t>input_hash</t>
         </is>
       </c>
-      <c r="T101" s="19" t="inlineStr">
+      <c r="U101" s="19" t="inlineStr">
         <is>
           <t>validator_result</t>
         </is>
@@ -28784,65 +28830,70 @@
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>STRING(300)</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
+          <t>HASH</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
           <t>STRING(100)</t>
         </is>
       </c>
-      <c r="J102" s="6" t="inlineStr">
+      <c r="K102" s="6" t="inlineStr">
         <is>
           <t>STRING(60)</t>
         </is>
       </c>
-      <c r="K102" s="6" t="inlineStr">
+      <c r="L102" s="6" t="inlineStr">
         <is>
           <t>STRING(20)</t>
         </is>
       </c>
-      <c r="L102" s="6" t="inlineStr">
+      <c r="M102" s="6" t="inlineStr">
         <is>
           <t>DECIMAL(5,4)</t>
         </is>
       </c>
-      <c r="M102" s="6" t="inlineStr">
+      <c r="N102" s="6" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="N102" s="6" t="inlineStr">
+      <c r="O102" s="6" t="inlineStr">
         <is>
           <t>REF(actor)</t>
         </is>
       </c>
-      <c r="O102" s="6" t="inlineStr">
+      <c r="P102" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP_TZ</t>
         </is>
       </c>
-      <c r="P102" s="6" t="inlineStr">
+      <c r="Q102" s="6" t="inlineStr">
         <is>
           <t>REF(event)</t>
         </is>
       </c>
-      <c r="Q102" s="6" t="inlineStr">
+      <c r="R102" s="6" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="R102" s="6" t="inlineStr">
+      <c r="S102" s="6" t="inlineStr">
         <is>
           <t>STRING(20)</t>
         </is>
       </c>
-      <c r="S102" s="6" t="inlineStr">
+      <c r="T102" s="6" t="inlineStr">
         <is>
           <t>HASH</t>
         </is>
       </c>
-      <c r="T102" s="6" t="inlineStr">
+      <c r="U102" s="6" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
@@ -28886,65 +28937,70 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
+          <t>NOT NULL / 보관 관리 내용 참조(29절). 파기돼도 참조는 남는다 / rev.2.4 (옛 source_quote)</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL / 인용이 파기돼도 남는다 / rev.2.4 신규</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="I103" s="3" t="inlineStr">
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / 근거 강도 아님</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>PENDING / ACCEPTED / REJECTED / SUPERSEDED - 한 방향 한 번</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="inlineStr">
         <is>
           <t>NULL 허용</t>
         </is>
       </c>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용</t>
+        </is>
+      </c>
+      <c r="Q103" s="3" t="inlineStr">
+        <is>
+          <t>NULL 허용 / ACCEPTED 면 필수</t>
+        </is>
+      </c>
+      <c r="R103" s="3" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / 근거 강도 아님</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>PENDING / ACCEPTED / REJECTED / SUPERSEDED - 한 방향 한 번</t>
-        </is>
-      </c>
-      <c r="N103" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="O103" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용</t>
-        </is>
-      </c>
-      <c r="P103" s="3" t="inlineStr">
-        <is>
-          <t>NULL 허용 / ACCEPTED 면 필수</t>
-        </is>
-      </c>
-      <c r="Q103" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="R103" s="3" t="inlineStr">
+      <c r="S103" s="3" t="inlineStr">
         <is>
           <t>NOT NULL / 어느 추출 계약으로 뽑았나 / rev.2.3 신규</t>
         </is>
       </c>
-      <c r="S103" s="3" t="inlineStr">
+      <c r="T103" s="3" t="inlineStr">
         <is>
           <t>NOT NULL / 무엇을 넣고 뽑았나 / rev.2.3 신규</t>
         </is>
       </c>
-      <c r="T103" s="3" t="inlineStr">
+      <c r="U103" s="3" t="inlineStr">
         <is>
           <t>NOT NULL / docs/05 4.6 검사별 결과 / model_confidence 와 다르다 / rev.2.3 신규</t>
         </is>
@@ -28986,67 +29042,64 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>40피트 1회 95,000원입니다 (합성)</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="n"/>
+      <c r="J104" s="3" t="inlineStr">
         <is>
           <t>body:3</t>
         </is>
       </c>
-      <c r="J104" s="3" t="inlineStr">
+      <c r="K104" s="3" t="inlineStr">
         <is>
           <t>(모델 판)</t>
         </is>
       </c>
-      <c r="K104" s="3" t="inlineStr">
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>p-v1</t>
         </is>
       </c>
-      <c r="L104" s="3" t="inlineStr">
+      <c r="M104" s="3" t="inlineStr">
         <is>
           <t>0.8800</t>
         </is>
       </c>
-      <c r="M104" s="3" t="inlineStr">
+      <c r="N104" s="3" t="inlineStr">
         <is>
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="N104" s="3" t="inlineStr">
+      <c r="O104" s="3" t="inlineStr">
         <is>
           <t>ACT-USR-01</t>
         </is>
       </c>
-      <c r="O104" s="3" t="inlineStr">
+      <c r="P104" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T10:40+09:00</t>
         </is>
       </c>
-      <c r="P104" s="3" t="inlineStr">
+      <c r="Q104" s="3" t="inlineStr">
         <is>
           <t>EVT-000061</t>
         </is>
       </c>
-      <c r="Q104" s="3" t="inlineStr">
+      <c r="R104" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="R104" s="3" t="inlineStr">
+      <c r="S104" s="3" t="inlineStr">
         <is>
           <t>ex-1</t>
         </is>
       </c>
-      <c r="S104" s="3" t="inlineStr">
+      <c r="T104" s="3" t="inlineStr">
         <is>
           <t>(해시값)</t>
         </is>
       </c>
-      <c r="T104" s="3" t="inlineStr">
+      <c r="U104" s="3" t="inlineStr">
         <is>
           <t>[SCHEMA_OK, QUOTE_MATCHED]</t>
         </is>

--- a/docs/22_cera-logical-data-model.xlsx
+++ b/docs/22_cera-logical-data-model.xlsx
@@ -3707,7 +3707,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="n">
         <v>2</v>
@@ -5135,6 +5134,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -5430,6 +5430,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
@@ -5533,6 +5534,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
@@ -6015,12 +6017,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>OPEN - rev.2 신규</t>
+          <t>CLOSED - T-069 (2026-09-21)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>후보: recovery_run 계보의 뿌리 / 최초 계기 사건 / 컨테이너 집합 지문. T-069 에서 답한다</t>
+          <t>recovery_run 계보(previous_run_id)의 뿌리 실행 id. 새 표·새 컬럼 없음. 같은 사고의 재계산은 previous_run_id 를 이어받는다. 범위 참조는 존재하는 뿌리 실행 id (I-35·I-36). ExceptionCase 부활 없음</t>
         </is>
       </c>
     </row>
@@ -6156,6 +6158,8 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
@@ -6236,7 +6240,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>복구 맥락 식별자 (L-13)</t>
+          <t>(닫힘) 복구 맥락 식별자 (L-13) — 2026-09-21 T-069 CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/22_cera-logical-data-model.xlsx
+++ b/docs/22_cera-logical-data-model.xlsx
@@ -581,7 +581,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>rev.2.4 Q-44 · Q-45 사용자 결정 반영 (2026-09-21). 메일 근거 시각 규칙 + 기록·내용 분리 보관. 표 수 변화 없음. 흐름 검증 64개 PASS. (rev.2.3 T-081 DONE 위)</t>
+          <t>rev.2.5 T-080 물리 설계 검토 반영 (2026-09-22). 발송 시도 멱등·재시도·UNKNOWN 화해 · sent_at / external_thread_id 한 번 채움 · INBOUND drafted_by·current_status · 표기 정정. 표·컬럼 수 변화 없음. (rev.2.4 Q-44 · Q-45 위)</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>CONTROLLED_UPDATE (thread_status · last_activity_at)</t>
+          <t>CONTROLLED_UPDATE (thread_status · last_activity_at) + external_thread_id 한 번 채움</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>IMMUTABLE_AFTER_CREATE + CACHE_UPDATE</t>
+          <t>IMMUTABLE_AFTER_CREATE + CACHE_UPDATE + sent_at 한 번 채움</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (결과 5컬럼)</t>
+          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (결과 5컬럼 · UNKNOWN 화해 한 번)</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -5134,7 +5134,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -5430,7 +5429,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
@@ -5534,7 +5532,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
@@ -6158,8 +6155,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
@@ -13466,7 +13461,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>SUBJECT / CONTEXT</t>
+          <t>NOT NULL / SUBJECT / CONTEXT (rev.2.5 표기 정정 — I-8)</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14495,7 @@
       </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL / 계산 결과</t>
+          <t>NOT NULL / 계산 결과 / 강도 0·1·2·3 (docs/05 3.3, rev.2.5)</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
@@ -14646,7 +14641,7 @@
       </c>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
@@ -14661,7 +14656,7 @@
       </c>
       <c r="Z58" s="3" t="inlineStr">
         <is>
-          <t>SOURCE_EVENT_TIME</t>
+          <t>EVENT_TIME</t>
         </is>
       </c>
       <c r="AA58" s="3" t="inlineStr">
@@ -14796,7 +14791,7 @@
       </c>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
@@ -14811,7 +14806,7 @@
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
-          <t>SOURCE_EVENT_TIME</t>
+          <t>EVENT_TIME</t>
         </is>
       </c>
       <c r="AA59" s="3" t="inlineStr">
@@ -24554,7 +24549,7 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>CONTROLLED_UPDATE (thread_status · last_activity_at)</t>
+          <t>CONTROLLED_UPDATE (thread_status · last_activity_at) + external_thread_id 한 번 채움</t>
         </is>
       </c>
     </row>
@@ -24789,7 +24784,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용</t>
+          <t>NULL 허용 / 첫 발송 뒤 NULL → 값 한 번(rev.2.5)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -24901,6 +24896,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="n">
         <v>2</v>
@@ -25538,6 +25534,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="8" t="n">
         <v>3</v>
@@ -25589,7 +25586,7 @@
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>IMMUTABLE_AFTER_CREATE + CACHE_UPDATE</t>
+          <t>IMMUTABLE_AFTER_CREATE + CACHE_UPDATE + sent_at 한 번 채움</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25986,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL / 캐시</t>
+          <t>OUTBOUND 면 NOT NULL / 캐시 / INBOUND 는 NULL(rev.2.5)</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -25999,7 +25996,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>AI_DRAFT / HUMAN / TEMPLATE</t>
+          <t>OUTBOUND 면 필수 / AI_DRAFT / HUMAN / TEMPLATE / INBOUND 는 NULL(rev.2.5)</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -26009,7 +26006,7 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>NULL 허용</t>
+          <t>NULL 허용 / 발송 성공 확인 뒤 NULL → 값 한 번(rev.2.5)</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
@@ -26282,6 +26279,7 @@
       <c r="T36" s="3" t="n"/>
       <c r="U36" s="3" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="8" t="n">
         <v>4</v>
@@ -26631,6 +26629,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="8" t="n">
         <v>5</v>
@@ -26795,6 +26794,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="8" t="n">
         <v>6</v>
@@ -27284,6 +27284,7 @@
       </c>
       <c r="O65" s="3" t="n"/>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="8" t="n">
         <v>7</v>
@@ -27633,6 +27634,7 @@
         </is>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="8" t="n">
         <v>8</v>
@@ -27684,7 +27686,7 @@
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (결과 5컬럼)</t>
+          <t>IMMUTABLE_AFTER_CREATE + CONTROLLED_UPDATE (결과 5컬럼 · UNKNOWN 화해 한 번)</t>
         </is>
       </c>
     </row>
@@ -27971,7 +27973,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL / 채널+메시지+내용지문+(있으면)승인</t>
+          <t>NOT NULL / UNIQUE / 시도마다 다름: 메시지 + 시도 번호(rev.2.5)</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -27996,7 +27998,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>NULL = 결과 기록 전 / SUCCESS / RETRYABLE_FAILURE / PERMANENT_FAILURE / UNKNOWN - 한 번만</t>
+          <t>NULL = 결과 기록 전 / SUCCESS / RETRYABLE_FAILURE / PERMANENT_FAILURE / UNKNOWN - NULL → 결과 한 번, UNKNOWN 은 화해로 SUCCESS · RETRYABLE_FAILURE 한 번 더(rev.2.5)</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
@@ -28048,7 +28050,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>MOCK:MSG-000020:(해시값):APV-0001</t>
+          <t>(해시: MSG-000020 · 시도 1)</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -28113,7 +28115,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>MOCK:MSG-000030:(해시값)</t>
+          <t>(해시: MSG-000030 · 시도 1)</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -28154,6 +28156,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="8" t="n">
         <v>9</v>
@@ -28503,6 +28506,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="8" t="n">
         <v>10</v>
